--- a/research/traditional_assets/database/data/colombia/colombia_retail_general.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1118138366946013</v>
+        <v>0.1114517382661703</v>
       </c>
       <c r="C2">
-        <v>1401.727347911423</v>
+        <v>1391.627530698355</v>
       </c>
       <c r="D2">
-        <v>1190.327347911423</v>
+        <v>1196.892530698355</v>
       </c>
       <c r="E2">
-        <v>-1049.3</v>
+        <v>-1032.635</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.665</v>
       </c>
       <c r="G2">
         <v>211.4</v>
@@ -1451,28 +1451,28 @@
         <v>241.475</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8382494999999999</v>
       </c>
       <c r="N2">
-        <v>241.475</v>
+        <v>240.6367505</v>
       </c>
       <c r="O2">
-        <v>84.51625</v>
+        <v>84.222862675</v>
       </c>
       <c r="P2">
-        <v>156.95875</v>
+        <v>156.413887825</v>
       </c>
       <c r="Q2">
-        <v>235.35875</v>
+        <v>234.813887825</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1118138366946013</v>
+        <v>0.1122472608749195</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9668886092550261</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>288.070556558638</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1114517382661703</v>
+        <v>0.1110896398377391</v>
       </c>
       <c r="C3">
-        <v>1391.627530698355</v>
+        <v>1381.600534912254</v>
       </c>
       <c r="D3">
-        <v>1196.892530698355</v>
+        <v>1203.530534912253</v>
       </c>
       <c r="E3">
-        <v>-1032.635</v>
+        <v>-1015.97</v>
       </c>
       <c r="F3">
-        <v>16.665</v>
+        <v>33.33</v>
       </c>
       <c r="G3">
         <v>211.4</v>
@@ -1533,28 +1533,28 @@
         <v>241.475</v>
       </c>
       <c r="M3">
-        <v>0.8382494999999999</v>
+        <v>1.676499</v>
       </c>
       <c r="N3">
-        <v>240.6367505</v>
+        <v>239.798501</v>
       </c>
       <c r="O3">
-        <v>84.222862675</v>
+        <v>83.92947534999999</v>
       </c>
       <c r="P3">
-        <v>156.413887825</v>
+        <v>155.86902565</v>
       </c>
       <c r="Q3">
-        <v>234.813887825</v>
+        <v>234.26902565</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1122472608749195</v>
+        <v>0.1126895304466726</v>
       </c>
       <c r="T3">
-        <v>0.9668886092550261</v>
+        <v>0.9733241704131178</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>288.070556558638</v>
+        <v>144.035278279319</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1110896398377391</v>
+        <v>0.110727541409308</v>
       </c>
       <c r="C4">
-        <v>1381.600534912254</v>
+        <v>1371.647578920101</v>
       </c>
       <c r="D4">
-        <v>1203.530534912253</v>
+        <v>1210.242578920101</v>
       </c>
       <c r="E4">
-        <v>-1015.97</v>
+        <v>-999.3049999999999</v>
       </c>
       <c r="F4">
-        <v>33.33</v>
+        <v>49.995</v>
       </c>
       <c r="G4">
         <v>211.4</v>
@@ -1615,28 +1615,28 @@
         <v>241.475</v>
       </c>
       <c r="M4">
-        <v>1.676499</v>
+        <v>2.5147485</v>
       </c>
       <c r="N4">
-        <v>239.798501</v>
+        <v>238.9602515</v>
       </c>
       <c r="O4">
-        <v>83.92947534999999</v>
+        <v>83.63608802499999</v>
       </c>
       <c r="P4">
-        <v>155.86902565</v>
+        <v>155.324163475</v>
       </c>
       <c r="Q4">
-        <v>234.26902565</v>
+        <v>233.724163475</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1126895304466726</v>
+        <v>0.1131409189786681</v>
       </c>
       <c r="T4">
-        <v>0.9733241704131178</v>
+        <v>0.9798924235538505</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.035278279319</v>
+        <v>96.02351885287933</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.110727541409308</v>
+        <v>0.1103654429808769</v>
       </c>
       <c r="C5">
-        <v>1371.647578920101</v>
+        <v>1361.769908420452</v>
       </c>
       <c r="D5">
-        <v>1210.242578920101</v>
+        <v>1217.029908420452</v>
       </c>
       <c r="E5">
-        <v>-999.3049999999999</v>
+        <v>-982.64</v>
       </c>
       <c r="F5">
-        <v>49.995</v>
+        <v>66.66</v>
       </c>
       <c r="G5">
         <v>211.4</v>
@@ -1697,28 +1697,28 @@
         <v>241.475</v>
       </c>
       <c r="M5">
-        <v>2.5147485</v>
+        <v>3.352997999999999</v>
       </c>
       <c r="N5">
-        <v>238.9602515</v>
+        <v>238.122002</v>
       </c>
       <c r="O5">
-        <v>83.63608802499999</v>
+        <v>83.34270069999999</v>
       </c>
       <c r="P5">
-        <v>155.324163475</v>
+        <v>154.7793013</v>
       </c>
       <c r="Q5">
-        <v>233.724163475</v>
+        <v>233.1793013</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1131409189786681</v>
+        <v>0.1136017114384135</v>
       </c>
       <c r="T5">
-        <v>0.9798924235538505</v>
+        <v>0.9865975153016819</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.02351885287933</v>
+        <v>72.01763913965951</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1103654429808769</v>
+        <v>0.1100033445524458</v>
       </c>
       <c r="C6">
-        <v>1361.769908420452</v>
+        <v>1351.968797214169</v>
       </c>
       <c r="D6">
-        <v>1217.029908420452</v>
+        <v>1223.893797214169</v>
       </c>
       <c r="E6">
-        <v>-982.64</v>
+        <v>-965.9749999999999</v>
       </c>
       <c r="F6">
-        <v>66.66</v>
+        <v>83.325</v>
       </c>
       <c r="G6">
         <v>211.4</v>
@@ -1779,28 +1779,28 @@
         <v>241.475</v>
       </c>
       <c r="M6">
-        <v>3.352997999999999</v>
+        <v>4.1912475</v>
       </c>
       <c r="N6">
-        <v>238.122002</v>
+        <v>237.2837525</v>
       </c>
       <c r="O6">
-        <v>83.34270069999999</v>
+        <v>83.049313375</v>
       </c>
       <c r="P6">
-        <v>154.7793013</v>
+        <v>154.234439125</v>
       </c>
       <c r="Q6">
-        <v>233.1793013</v>
+        <v>232.634439125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1136017114384135</v>
+        <v>0.1140722047920482</v>
       </c>
       <c r="T6">
-        <v>0.9865975153016819</v>
+        <v>0.9934437668757835</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.01763913965951</v>
+        <v>57.61411131172759</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1100033445524458</v>
+        <v>0.1096412461240147</v>
       </c>
       <c r="C7">
-        <v>1351.968797214169</v>
+        <v>1342.245548001379</v>
       </c>
       <c r="D7">
-        <v>1223.893797214169</v>
+        <v>1230.835548001379</v>
       </c>
       <c r="E7">
-        <v>-965.9749999999999</v>
+        <v>-949.3099999999999</v>
       </c>
       <c r="F7">
-        <v>83.325</v>
+        <v>99.99000000000001</v>
       </c>
       <c r="G7">
         <v>211.4</v>
@@ -1861,28 +1861,28 @@
         <v>241.475</v>
       </c>
       <c r="M7">
-        <v>4.1912475</v>
+        <v>5.029497</v>
       </c>
       <c r="N7">
-        <v>237.2837525</v>
+        <v>236.445503</v>
       </c>
       <c r="O7">
-        <v>83.049313375</v>
+        <v>82.75592605</v>
       </c>
       <c r="P7">
-        <v>154.234439125</v>
+        <v>153.68957695</v>
       </c>
       <c r="Q7">
-        <v>232.634439125</v>
+        <v>232.08957695</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1140722047920482</v>
+        <v>0.1145527086425689</v>
       </c>
       <c r="T7">
-        <v>0.9934437668757835</v>
+        <v>1.000435683376994</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.61411131172759</v>
+        <v>48.01175942643966</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1096412461240147</v>
+        <v>0.1092791476955836</v>
       </c>
       <c r="C8">
-        <v>1342.245548001379</v>
+        <v>1332.601493205712</v>
       </c>
       <c r="D8">
-        <v>1230.835548001379</v>
+        <v>1237.856493205712</v>
       </c>
       <c r="E8">
-        <v>-949.3099999999999</v>
+        <v>-932.645</v>
       </c>
       <c r="F8">
-        <v>99.98999999999999</v>
+        <v>116.655</v>
       </c>
       <c r="G8">
         <v>211.4</v>
@@ -1943,28 +1943,28 @@
         <v>241.475</v>
       </c>
       <c r="M8">
-        <v>5.029496999999999</v>
+        <v>5.867746499999999</v>
       </c>
       <c r="N8">
-        <v>236.445503</v>
+        <v>235.6072535</v>
       </c>
       <c r="O8">
-        <v>82.75592605</v>
+        <v>82.46253872499999</v>
       </c>
       <c r="P8">
-        <v>153.68957695</v>
+        <v>153.144714775</v>
       </c>
       <c r="Q8">
-        <v>232.08957695</v>
+        <v>231.544714775</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1145527086425689</v>
+        <v>0.1150435459092297</v>
       </c>
       <c r="T8">
-        <v>1.000435683376994</v>
+        <v>1.007577963673929</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.01175942643967</v>
+        <v>41.152936651234</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1092791476955836</v>
+        <v>0.1089170492671525</v>
       </c>
       <c r="C9">
-        <v>1332.601493205712</v>
+        <v>1323.037995826911</v>
       </c>
       <c r="D9">
-        <v>1237.856493205712</v>
+        <v>1244.957995826911</v>
       </c>
       <c r="E9">
-        <v>-932.645</v>
+        <v>-915.98</v>
       </c>
       <c r="F9">
-        <v>116.655</v>
+        <v>133.32</v>
       </c>
       <c r="G9">
         <v>211.4</v>
@@ -2025,28 +2025,28 @@
         <v>241.475</v>
       </c>
       <c r="M9">
-        <v>5.867746500000001</v>
+        <v>6.705995999999999</v>
       </c>
       <c r="N9">
-        <v>235.6072535</v>
+        <v>234.769004</v>
       </c>
       <c r="O9">
-        <v>82.46253872499999</v>
+        <v>82.16915139999999</v>
       </c>
       <c r="P9">
-        <v>153.144714775</v>
+        <v>152.5998526</v>
       </c>
       <c r="Q9">
-        <v>231.544714775</v>
+        <v>230.9998526</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1150435459092297</v>
+        <v>0.1155450535512527</v>
       </c>
       <c r="T9">
-        <v>1.007577963673929</v>
+        <v>1.014875510933841</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.15293665123399</v>
+        <v>36.00881956982975</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1089170492671525</v>
+        <v>0.1085549508387214</v>
       </c>
       <c r="C10">
-        <v>1323.037995826911</v>
+        <v>1313.556450322958</v>
       </c>
       <c r="D10">
-        <v>1244.957995826911</v>
+        <v>1252.141450322958</v>
       </c>
       <c r="E10">
-        <v>-915.98</v>
+        <v>-899.3149999999999</v>
       </c>
       <c r="F10">
-        <v>133.32</v>
+        <v>149.985</v>
       </c>
       <c r="G10">
         <v>211.4</v>
@@ -2107,28 +2107,28 @@
         <v>241.475</v>
       </c>
       <c r="M10">
-        <v>6.705995999999999</v>
+        <v>7.544245499999999</v>
       </c>
       <c r="N10">
-        <v>234.769004</v>
+        <v>233.9307545</v>
       </c>
       <c r="O10">
-        <v>82.16915139999999</v>
+        <v>81.87576407499999</v>
       </c>
       <c r="P10">
-        <v>152.5998526</v>
+        <v>152.054990425</v>
       </c>
       <c r="Q10">
-        <v>230.9998526</v>
+        <v>230.454990425</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1155450535512527</v>
+        <v>0.1160575833392543</v>
       </c>
       <c r="T10">
-        <v>1.014875510933841</v>
+        <v>1.022333443847816</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.00881956982975</v>
+        <v>32.00783961762644</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1085549508387214</v>
+        <v>0.1081928524102903</v>
       </c>
       <c r="C11">
-        <v>1313.556450322958</v>
+        <v>1304.15828352292</v>
       </c>
       <c r="D11">
-        <v>1252.141450322958</v>
+        <v>1259.40828352292</v>
       </c>
       <c r="E11">
-        <v>-899.3149999999999</v>
+        <v>-882.65</v>
       </c>
       <c r="F11">
-        <v>149.985</v>
+        <v>166.65</v>
       </c>
       <c r="G11">
         <v>211.4</v>
@@ -2189,28 +2189,28 @@
         <v>241.475</v>
       </c>
       <c r="M11">
-        <v>7.544245499999999</v>
+        <v>8.382494999999999</v>
       </c>
       <c r="N11">
-        <v>233.9307545</v>
+        <v>233.092505</v>
       </c>
       <c r="O11">
-        <v>81.87576407499999</v>
+        <v>81.58237674999999</v>
       </c>
       <c r="P11">
-        <v>152.054990425</v>
+        <v>151.51012825</v>
       </c>
       <c r="Q11">
-        <v>230.454990425</v>
+        <v>229.91012825</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1160575833392543</v>
+        <v>0.1165815026781003</v>
       </c>
       <c r="T11">
-        <v>1.022333443847816</v>
+        <v>1.029957108604325</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.00783961762644</v>
+        <v>28.8070556558638</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1081928524102903</v>
+        <v>0.1078307539818592</v>
       </c>
       <c r="C12">
-        <v>1304.15828352292</v>
+        <v>1294.844955571757</v>
       </c>
       <c r="D12">
-        <v>1259.40828352292</v>
+        <v>1266.759955571757</v>
       </c>
       <c r="E12">
-        <v>-882.65</v>
+        <v>-865.9849999999999</v>
       </c>
       <c r="F12">
-        <v>166.65</v>
+        <v>183.315</v>
       </c>
       <c r="G12">
         <v>211.4</v>
@@ -2271,28 +2271,28 @@
         <v>241.475</v>
       </c>
       <c r="M12">
-        <v>8.382495</v>
+        <v>9.220744499999999</v>
       </c>
       <c r="N12">
-        <v>233.092505</v>
+        <v>232.2542555</v>
       </c>
       <c r="O12">
-        <v>81.58237674999999</v>
+        <v>81.288989425</v>
       </c>
       <c r="P12">
-        <v>151.51012825</v>
+        <v>150.965266075</v>
       </c>
       <c r="Q12">
-        <v>229.91012825</v>
+        <v>229.365266075</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1165815026781003</v>
+        <v>0.1171171954852351</v>
       </c>
       <c r="T12">
-        <v>1.029957108604325</v>
+        <v>1.037752091669969</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.8070556558638</v>
+        <v>26.18823241442164</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1078307539818592</v>
+        <v>0.1074686555534281</v>
       </c>
       <c r="C13">
-        <v>1294.844955571757</v>
+        <v>1285.617960908433</v>
       </c>
       <c r="D13">
-        <v>1266.759955571757</v>
+        <v>1274.197960908433</v>
       </c>
       <c r="E13">
-        <v>-865.9849999999999</v>
+        <v>-849.3199999999999</v>
       </c>
       <c r="F13">
-        <v>183.315</v>
+        <v>199.98</v>
       </c>
       <c r="G13">
         <v>211.4</v>
@@ -2353,28 +2353,28 @@
         <v>241.475</v>
       </c>
       <c r="M13">
-        <v>9.220744499999999</v>
+        <v>10.058994</v>
       </c>
       <c r="N13">
-        <v>232.2542555</v>
+        <v>231.416006</v>
       </c>
       <c r="O13">
-        <v>81.288989425</v>
+        <v>80.99560209999999</v>
       </c>
       <c r="P13">
-        <v>150.965266075</v>
+        <v>150.4204039</v>
       </c>
       <c r="Q13">
-        <v>229.365266075</v>
+        <v>228.8204039</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1171171954852351</v>
+        <v>0.1176650631288955</v>
       </c>
       <c r="T13">
-        <v>1.037752091669969</v>
+        <v>1.04572423344165</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.18823241442164</v>
+        <v>24.00587971321983</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1074686555534281</v>
+        <v>0.107106557124997</v>
       </c>
       <c r="C14">
-        <v>1285.617960908433</v>
+        <v>1276.478829278669</v>
       </c>
       <c r="D14">
-        <v>1274.197960908433</v>
+        <v>1281.723829278669</v>
       </c>
       <c r="E14">
-        <v>-849.3199999999999</v>
+        <v>-832.655</v>
       </c>
       <c r="F14">
-        <v>199.98</v>
+        <v>216.645</v>
       </c>
       <c r="G14">
         <v>211.4</v>
@@ -2435,28 +2435,28 @@
         <v>241.475</v>
       </c>
       <c r="M14">
-        <v>10.058994</v>
+        <v>10.8972435</v>
       </c>
       <c r="N14">
-        <v>231.416006</v>
+        <v>230.5777565</v>
       </c>
       <c r="O14">
-        <v>80.99560209999999</v>
+        <v>80.70221477499999</v>
       </c>
       <c r="P14">
-        <v>150.4204039</v>
+        <v>149.875541725</v>
       </c>
       <c r="Q14">
-        <v>228.8204039</v>
+        <v>228.275541725</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1176650631288955</v>
+        <v>0.118225525431031</v>
       </c>
       <c r="T14">
-        <v>1.04572423344165</v>
+        <v>1.053879642840266</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.00587971321983</v>
+        <v>22.15927358143369</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.107106557124997</v>
+        <v>0.1067444586965659</v>
       </c>
       <c r="C15">
-        <v>1276.478829278669</v>
+        <v>1267.429126783815</v>
       </c>
       <c r="D15">
-        <v>1281.723829278669</v>
+        <v>1289.339126783815</v>
       </c>
       <c r="E15">
-        <v>-832.655</v>
+        <v>-815.9899999999999</v>
       </c>
       <c r="F15">
-        <v>216.645</v>
+        <v>233.31</v>
       </c>
       <c r="G15">
         <v>211.4</v>
@@ -2517,28 +2517,28 @@
         <v>241.475</v>
       </c>
       <c r="M15">
-        <v>10.8972435</v>
+        <v>11.735493</v>
       </c>
       <c r="N15">
-        <v>230.5777565</v>
+        <v>229.739507</v>
       </c>
       <c r="O15">
-        <v>80.70221477499999</v>
+        <v>80.40882744999999</v>
       </c>
       <c r="P15">
-        <v>149.875541725</v>
+        <v>149.33067955</v>
       </c>
       <c r="Q15">
-        <v>228.275541725</v>
+        <v>227.73067955</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.118225525431031</v>
+        <v>0.1187990217401929</v>
       </c>
       <c r="T15">
-        <v>1.053879642840266</v>
+        <v>1.062224712922571</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.15927358143369</v>
+        <v>20.576468325617</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1067444586965659</v>
+        <v>0.1063823602681348</v>
       </c>
       <c r="C16">
-        <v>1267.429126783815</v>
+        <v>1258.470456967335</v>
       </c>
       <c r="D16">
-        <v>1289.339126783815</v>
+        <v>1297.045456967335</v>
       </c>
       <c r="E16">
-        <v>-815.9899999999999</v>
+        <v>-799.3249999999999</v>
       </c>
       <c r="F16">
-        <v>233.31</v>
+        <v>249.9750000000001</v>
       </c>
       <c r="G16">
         <v>211.4</v>
@@ -2599,28 +2599,28 @@
         <v>241.475</v>
       </c>
       <c r="M16">
-        <v>11.735493</v>
+        <v>12.5737425</v>
       </c>
       <c r="N16">
-        <v>229.739507</v>
+        <v>228.9012575</v>
       </c>
       <c r="O16">
-        <v>80.40882744999999</v>
+        <v>80.11544012499999</v>
       </c>
       <c r="P16">
-        <v>149.33067955</v>
+        <v>148.785817375</v>
       </c>
       <c r="Q16">
-        <v>227.73067955</v>
+        <v>227.185817375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1187990217401929</v>
+        <v>0.1193860120801586</v>
       </c>
       <c r="T16">
-        <v>1.062224712922571</v>
+        <v>1.070766137595048</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.576468325617</v>
+        <v>19.20470377057586</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1063823602681348</v>
+        <v>0.1060202618397037</v>
       </c>
       <c r="C17">
-        <v>1258.470456967335</v>
+        <v>1249.604461940474</v>
       </c>
       <c r="D17">
-        <v>1297.045456967335</v>
+        <v>1304.844461940474</v>
       </c>
       <c r="E17">
-        <v>-799.3249999999999</v>
+        <v>-782.66</v>
       </c>
       <c r="F17">
-        <v>249.975</v>
+        <v>266.64</v>
       </c>
       <c r="G17">
         <v>211.4</v>
@@ -2681,28 +2681,28 @@
         <v>241.475</v>
       </c>
       <c r="M17">
-        <v>12.5737425</v>
+        <v>13.411992</v>
       </c>
       <c r="N17">
-        <v>228.9012575</v>
+        <v>228.063008</v>
       </c>
       <c r="O17">
-        <v>80.11544012499999</v>
+        <v>79.82205279999999</v>
       </c>
       <c r="P17">
-        <v>148.785817375</v>
+        <v>148.2409552</v>
       </c>
       <c r="Q17">
-        <v>227.185817375</v>
+        <v>226.6409552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1193860120801586</v>
+        <v>0.1199869783805996</v>
       </c>
       <c r="T17">
-        <v>1.070766137595048</v>
+        <v>1.079510929521632</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.20470377057586</v>
+        <v>18.00440978491488</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1060202618397037</v>
+        <v>0.1056581634112726</v>
       </c>
       <c r="C18">
-        <v>1249.604461940474</v>
+        <v>1240.832823548804</v>
       </c>
       <c r="D18">
-        <v>1304.844461940474</v>
+        <v>1312.737823548804</v>
       </c>
       <c r="E18">
-        <v>-782.66</v>
+        <v>-765.9949999999999</v>
       </c>
       <c r="F18">
-        <v>266.64</v>
+        <v>283.305</v>
       </c>
       <c r="G18">
         <v>211.4</v>
@@ -2763,28 +2763,28 @@
         <v>241.475</v>
       </c>
       <c r="M18">
-        <v>13.411992</v>
+        <v>14.2502415</v>
       </c>
       <c r="N18">
-        <v>228.063008</v>
+        <v>227.2247585</v>
       </c>
       <c r="O18">
-        <v>79.82205279999999</v>
+        <v>79.528665475</v>
       </c>
       <c r="P18">
-        <v>148.2409552</v>
+        <v>147.696093025</v>
       </c>
       <c r="Q18">
-        <v>226.6409552</v>
+        <v>226.096093025</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1199869783805996</v>
+        <v>0.1206024257967139</v>
       </c>
       <c r="T18">
-        <v>1.079510929521632</v>
+        <v>1.088466439325964</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.00440978491488</v>
+        <v>16.94532685639047</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1056581634112726</v>
+        <v>0.1052960649828415</v>
       </c>
       <c r="C19">
-        <v>1240.832823548804</v>
+        <v>1232.157264581352</v>
       </c>
       <c r="D19">
-        <v>1312.737823548804</v>
+        <v>1320.727264581352</v>
       </c>
       <c r="E19">
-        <v>-765.9949999999999</v>
+        <v>-749.3299999999999</v>
       </c>
       <c r="F19">
-        <v>283.305</v>
+        <v>299.97</v>
       </c>
       <c r="G19">
         <v>211.4</v>
@@ -2845,28 +2845,28 @@
         <v>241.475</v>
       </c>
       <c r="M19">
-        <v>14.2502415</v>
+        <v>15.088491</v>
       </c>
       <c r="N19">
-        <v>227.2247585</v>
+        <v>226.386509</v>
       </c>
       <c r="O19">
-        <v>79.528665475</v>
+        <v>79.23527814999998</v>
       </c>
       <c r="P19">
-        <v>147.696093025</v>
+        <v>147.15123085</v>
       </c>
       <c r="Q19">
-        <v>226.096093025</v>
+        <v>225.55123085</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1206024257967139</v>
+        <v>0.1212328841254164</v>
       </c>
       <c r="T19">
-        <v>1.088466439325964</v>
+        <v>1.097640376198695</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.94532685639047</v>
+        <v>16.00391980881322</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1052960649828415</v>
+        <v>0.1049339665544104</v>
       </c>
       <c r="C20">
-        <v>1232.157264581352</v>
+        <v>1223.579550024161</v>
       </c>
       <c r="D20">
-        <v>1320.727264581352</v>
+        <v>1328.814550024161</v>
       </c>
       <c r="E20">
-        <v>-749.3299999999999</v>
+        <v>-732.665</v>
       </c>
       <c r="F20">
-        <v>299.97</v>
+        <v>316.635</v>
       </c>
       <c r="G20">
         <v>211.4</v>
@@ -2927,28 +2927,28 @@
         <v>241.475</v>
       </c>
       <c r="M20">
-        <v>15.088491</v>
+        <v>15.9267405</v>
       </c>
       <c r="N20">
-        <v>226.386509</v>
+        <v>225.5482595</v>
       </c>
       <c r="O20">
-        <v>79.23527814999998</v>
+        <v>78.941890825</v>
       </c>
       <c r="P20">
-        <v>147.15123085</v>
+        <v>146.606368675</v>
       </c>
       <c r="Q20">
-        <v>225.55123085</v>
+        <v>225.006368675</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1212328841254164</v>
+        <v>0.1218789093264326</v>
       </c>
       <c r="T20">
-        <v>1.097640376198695</v>
+        <v>1.107040830031247</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.00391980881322</v>
+        <v>15.16160823992831</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1049339665544104</v>
+        <v>0.1045718681259793</v>
       </c>
       <c r="C21">
-        <v>1223.579550024161</v>
+        <v>1215.101488360182</v>
       </c>
       <c r="D21">
-        <v>1328.814550024161</v>
+        <v>1337.001488360181</v>
       </c>
       <c r="E21">
-        <v>-732.665</v>
+        <v>-716</v>
       </c>
       <c r="F21">
-        <v>316.635</v>
+        <v>333.3</v>
       </c>
       <c r="G21">
         <v>211.4</v>
@@ -3009,28 +3009,28 @@
         <v>241.475</v>
       </c>
       <c r="M21">
-        <v>15.9267405</v>
+        <v>16.76499</v>
       </c>
       <c r="N21">
-        <v>225.5482595</v>
+        <v>224.71001</v>
       </c>
       <c r="O21">
-        <v>78.941890825</v>
+        <v>78.64850349999999</v>
       </c>
       <c r="P21">
-        <v>146.606368675</v>
+        <v>146.0615065</v>
       </c>
       <c r="Q21">
-        <v>225.006368675</v>
+        <v>224.4615065</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1218789093264326</v>
+        <v>0.1225410851574741</v>
       </c>
       <c r="T21">
-        <v>1.107040830031247</v>
+        <v>1.116676295209612</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.16160823992831</v>
+        <v>14.4035278279319</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1045718681259793</v>
+        <v>0.1042097696975482</v>
       </c>
       <c r="C22">
-        <v>1215.101488360182</v>
+        <v>1206.724932917524</v>
       </c>
       <c r="D22">
-        <v>1337.001488360181</v>
+        <v>1345.289932917524</v>
       </c>
       <c r="E22">
-        <v>-716</v>
+        <v>-699.3349999999999</v>
       </c>
       <c r="F22">
-        <v>333.3</v>
+        <v>349.965</v>
       </c>
       <c r="G22">
         <v>211.4</v>
@@ -3091,28 +3091,28 @@
         <v>241.475</v>
       </c>
       <c r="M22">
-        <v>16.76499</v>
+        <v>17.6032395</v>
       </c>
       <c r="N22">
-        <v>224.71001</v>
+        <v>223.8717605</v>
       </c>
       <c r="O22">
-        <v>78.64850349999999</v>
+        <v>78.35511617499999</v>
       </c>
       <c r="P22">
-        <v>146.0615065</v>
+        <v>145.516644325</v>
       </c>
       <c r="Q22">
-        <v>224.4615065</v>
+        <v>223.916644325</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1225410851574741</v>
+        <v>0.1232200249336053</v>
       </c>
       <c r="T22">
-        <v>1.116676295209612</v>
+        <v>1.126555696215277</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.4035278279319</v>
+        <v>13.71764555041133</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1042097696975482</v>
+        <v>0.1038476712691171</v>
       </c>
       <c r="C23">
-        <v>1206.724932917524</v>
+        <v>1198.451783268164</v>
       </c>
       <c r="D23">
-        <v>1345.289932917524</v>
+        <v>1353.681783268164</v>
       </c>
       <c r="E23">
-        <v>-699.335</v>
+        <v>-682.67</v>
       </c>
       <c r="F23">
-        <v>349.965</v>
+        <v>366.63</v>
       </c>
       <c r="G23">
         <v>211.4</v>
@@ -3173,28 +3173,28 @@
         <v>241.475</v>
       </c>
       <c r="M23">
-        <v>17.6032395</v>
+        <v>18.441489</v>
       </c>
       <c r="N23">
-        <v>223.8717605</v>
+        <v>223.033511</v>
       </c>
       <c r="O23">
-        <v>78.35511617499999</v>
+        <v>78.06172884999999</v>
       </c>
       <c r="P23">
-        <v>145.516644325</v>
+        <v>144.97178215</v>
       </c>
       <c r="Q23">
-        <v>223.916644325</v>
+        <v>223.37178215</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1232200249336053</v>
+        <v>0.1239163734219449</v>
       </c>
       <c r="T23">
-        <v>1.126555696215277</v>
+        <v>1.136688415195447</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.71764555041133</v>
+        <v>13.09411620721082</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1038476712691171</v>
+        <v>0.1037098228406859</v>
       </c>
       <c r="C24">
-        <v>1198.451783268164</v>
+        <v>1185.009084723527</v>
       </c>
       <c r="D24">
-        <v>1353.681783268164</v>
+        <v>1356.904084723527</v>
       </c>
       <c r="E24">
-        <v>-682.67</v>
+        <v>-666.0049999999999</v>
       </c>
       <c r="F24">
-        <v>366.63</v>
+        <v>383.295</v>
       </c>
       <c r="G24">
         <v>211.4</v>
@@ -3255,45 +3255,45 @@
         <v>241.475</v>
       </c>
       <c r="M24">
-        <v>18.441489</v>
+        <v>19.854681</v>
       </c>
       <c r="N24">
-        <v>223.033511</v>
+        <v>221.620319</v>
       </c>
       <c r="O24">
-        <v>78.06172884999999</v>
+        <v>77.56711164999999</v>
       </c>
       <c r="P24">
-        <v>144.97178215</v>
+        <v>144.05320735</v>
       </c>
       <c r="Q24">
-        <v>223.37178215</v>
+        <v>222.45320735</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1239163734219449</v>
+        <v>0.1246308088840077</v>
       </c>
       <c r="T24">
-        <v>1.136688415195447</v>
+        <v>1.147084321681595</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.09411620721082</v>
+        <v>12.16211935109912</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1037098228406859</v>
+        <v>0.1033574744122548</v>
       </c>
       <c r="C25">
-        <v>1185.009084723527</v>
+        <v>1176.650617049106</v>
       </c>
       <c r="D25">
-        <v>1356.904084723527</v>
+        <v>1365.210617049106</v>
       </c>
       <c r="E25">
-        <v>-666.0049999999999</v>
+        <v>-649.3399999999999</v>
       </c>
       <c r="F25">
-        <v>383.295</v>
+        <v>399.96</v>
       </c>
       <c r="G25">
         <v>211.4</v>
@@ -3337,28 +3337,28 @@
         <v>241.475</v>
       </c>
       <c r="M25">
-        <v>19.854681</v>
+        <v>20.717928</v>
       </c>
       <c r="N25">
-        <v>221.620319</v>
+        <v>220.757072</v>
       </c>
       <c r="O25">
-        <v>77.56711164999999</v>
+        <v>77.26497519999999</v>
       </c>
       <c r="P25">
-        <v>144.05320735</v>
+        <v>143.4920968</v>
       </c>
       <c r="Q25">
-        <v>222.45320735</v>
+        <v>221.8920968</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1246308088840077</v>
+        <v>0.1253640452792827</v>
       </c>
       <c r="T25">
-        <v>1.147084321681595</v>
+        <v>1.157753804654221</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.16211935109912</v>
+        <v>11.65536437813665</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1033574744122548</v>
+        <v>0.1030051259838237</v>
       </c>
       <c r="C26">
-        <v>1176.650617049106</v>
+        <v>1168.394475645637</v>
       </c>
       <c r="D26">
-        <v>1365.210617049106</v>
+        <v>1373.619475645637</v>
       </c>
       <c r="E26">
-        <v>-649.3399999999999</v>
+        <v>-632.675</v>
       </c>
       <c r="F26">
-        <v>399.96</v>
+        <v>416.625</v>
       </c>
       <c r="G26">
         <v>211.4</v>
@@ -3419,28 +3419,28 @@
         <v>241.475</v>
       </c>
       <c r="M26">
-        <v>20.717928</v>
+        <v>21.581175</v>
       </c>
       <c r="N26">
-        <v>220.757072</v>
+        <v>219.893825</v>
       </c>
       <c r="O26">
-        <v>77.26497519999999</v>
+        <v>76.96283874999999</v>
       </c>
       <c r="P26">
-        <v>143.4920968</v>
+        <v>142.93098625</v>
       </c>
       <c r="Q26">
-        <v>221.8920968</v>
+        <v>221.33098625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1253640452792827</v>
+        <v>0.1261168346450983</v>
       </c>
       <c r="T26">
-        <v>1.157753804654221</v>
+        <v>1.168707807172784</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.65536437813666</v>
+        <v>11.18914980301119</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1030051259838237</v>
+        <v>0.1026527775553926</v>
       </c>
       <c r="C27">
-        <v>1168.394475645637</v>
+        <v>1160.242563032345</v>
       </c>
       <c r="D27">
-        <v>1373.619475645637</v>
+        <v>1382.132563032345</v>
       </c>
       <c r="E27">
-        <v>-632.675</v>
+        <v>-616.01</v>
       </c>
       <c r="F27">
-        <v>416.625</v>
+        <v>433.29</v>
       </c>
       <c r="G27">
         <v>211.4</v>
@@ -3501,28 +3501,28 @@
         <v>241.475</v>
       </c>
       <c r="M27">
-        <v>21.581175</v>
+        <v>22.444422</v>
       </c>
       <c r="N27">
-        <v>219.893825</v>
+        <v>219.030578</v>
       </c>
       <c r="O27">
-        <v>76.96283874999999</v>
+        <v>76.6607023</v>
       </c>
       <c r="P27">
-        <v>142.93098625</v>
+        <v>142.3698757</v>
       </c>
       <c r="Q27">
-        <v>221.33098625</v>
+        <v>220.7698757</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1261168346450983</v>
+        <v>0.1268899696694495</v>
       </c>
       <c r="T27">
-        <v>1.168707807172784</v>
+        <v>1.179957863813469</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.18914980301119</v>
+        <v>10.75879788751076</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1026527775553926</v>
+        <v>0.1023004291269615</v>
       </c>
       <c r="C28">
-        <v>1160.242563032345</v>
+        <v>1152.196829186475</v>
       </c>
       <c r="D28">
-        <v>1382.132563032345</v>
+        <v>1390.751829186476</v>
       </c>
       <c r="E28">
-        <v>-616.01</v>
+        <v>-599.3449999999999</v>
       </c>
       <c r="F28">
-        <v>433.29</v>
+        <v>449.955</v>
       </c>
       <c r="G28">
         <v>211.4</v>
@@ -3583,28 +3583,28 @@
         <v>241.475</v>
       </c>
       <c r="M28">
-        <v>22.444422</v>
+        <v>23.307669</v>
       </c>
       <c r="N28">
-        <v>219.030578</v>
+        <v>218.167331</v>
       </c>
       <c r="O28">
-        <v>76.6607023</v>
+        <v>76.35856584999999</v>
       </c>
       <c r="P28">
-        <v>142.3698757</v>
+        <v>141.80876515</v>
       </c>
       <c r="Q28">
-        <v>220.7698757</v>
+        <v>220.20876515</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1268899696694495</v>
+        <v>0.1276842864752898</v>
       </c>
       <c r="T28">
-        <v>1.179957863813469</v>
+        <v>1.191516141184037</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.75879788751076</v>
+        <v>10.36032389167703</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1023004291269615</v>
+        <v>0.1019480806985304</v>
       </c>
       <c r="C29">
-        <v>1152.196829186475</v>
+        <v>1144.259273032377</v>
       </c>
       <c r="D29">
-        <v>1390.751829186476</v>
+        <v>1399.479273032377</v>
       </c>
       <c r="E29">
-        <v>-599.3449999999999</v>
+        <v>-582.6799999999998</v>
       </c>
       <c r="F29">
-        <v>449.955</v>
+        <v>466.6200000000001</v>
       </c>
       <c r="G29">
         <v>211.4</v>
@@ -3665,28 +3665,28 @@
         <v>241.475</v>
       </c>
       <c r="M29">
-        <v>23.307669</v>
+        <v>24.170916</v>
       </c>
       <c r="N29">
-        <v>218.167331</v>
+        <v>217.304084</v>
       </c>
       <c r="O29">
-        <v>76.35856584999999</v>
+        <v>76.05642939999998</v>
       </c>
       <c r="P29">
-        <v>141.80876515</v>
+        <v>141.2476546</v>
       </c>
       <c r="Q29">
-        <v>220.20876515</v>
+        <v>219.6476546</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1276842864752898</v>
+        <v>0.1285006676368478</v>
       </c>
       <c r="T29">
-        <v>1.191516141184037</v>
+        <v>1.203395481814898</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.36032389167703</v>
+        <v>9.990312324117133</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1019480806985304</v>
+        <v>0.1019161822700993</v>
       </c>
       <c r="C30">
-        <v>1144.259273032377</v>
+        <v>1128.389786690394</v>
       </c>
       <c r="D30">
-        <v>1399.479273032377</v>
+        <v>1400.274786690394</v>
       </c>
       <c r="E30">
-        <v>-582.6799999999998</v>
+        <v>-566.0149999999999</v>
       </c>
       <c r="F30">
-        <v>466.6200000000001</v>
+        <v>483.2850000000001</v>
       </c>
       <c r="G30">
         <v>211.4</v>
@@ -3747,45 +3747,45 @@
         <v>241.475</v>
       </c>
       <c r="M30">
-        <v>24.170916</v>
+        <v>25.8557475</v>
       </c>
       <c r="N30">
-        <v>217.304084</v>
+        <v>215.6192525</v>
       </c>
       <c r="O30">
-        <v>76.05642939999998</v>
+        <v>75.46673837499999</v>
       </c>
       <c r="P30">
-        <v>141.2476546</v>
+        <v>140.152514125</v>
       </c>
       <c r="Q30">
-        <v>219.6476546</v>
+        <v>218.552514125</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1285006676368478</v>
+        <v>0.1293400454508441</v>
       </c>
       <c r="T30">
-        <v>1.203395481814898</v>
+        <v>1.215609451759305</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>9.990312324117133</v>
+        <v>9.339316142378014</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1019161822700993</v>
+        <v>0.1015748838416682</v>
       </c>
       <c r="C31">
-        <v>1128.389786690394</v>
+        <v>1120.293367226139</v>
       </c>
       <c r="D31">
-        <v>1400.274786690394</v>
+        <v>1408.843367226139</v>
       </c>
       <c r="E31">
-        <v>-566.015</v>
+        <v>-549.3499999999999</v>
       </c>
       <c r="F31">
-        <v>483.285</v>
+        <v>499.95</v>
       </c>
       <c r="G31">
         <v>211.4</v>
@@ -3829,28 +3829,28 @@
         <v>241.475</v>
       </c>
       <c r="M31">
-        <v>25.8557475</v>
+        <v>26.747325</v>
       </c>
       <c r="N31">
-        <v>215.6192525</v>
+        <v>214.727675</v>
       </c>
       <c r="O31">
-        <v>75.46673837499999</v>
+        <v>75.15468625</v>
       </c>
       <c r="P31">
-        <v>140.152514125</v>
+        <v>139.57298875</v>
       </c>
       <c r="Q31">
-        <v>218.552514125</v>
+        <v>217.97298875</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1293400454508441</v>
+        <v>0.1302034054880974</v>
       </c>
       <c r="T31">
-        <v>1.215609451759305</v>
+        <v>1.228172392273551</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.339316142378015</v>
+        <v>9.028005604298748</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1015748838416682</v>
+        <v>0.1012335854132371</v>
       </c>
       <c r="C32">
-        <v>1120.293367226139</v>
+        <v>1112.302459359191</v>
       </c>
       <c r="D32">
-        <v>1408.843367226139</v>
+        <v>1417.517459359191</v>
       </c>
       <c r="E32">
-        <v>-549.3499999999999</v>
+        <v>-532.6849999999999</v>
       </c>
       <c r="F32">
-        <v>499.95</v>
+        <v>516.615</v>
       </c>
       <c r="G32">
         <v>211.4</v>
@@ -3911,28 +3911,28 @@
         <v>241.475</v>
       </c>
       <c r="M32">
-        <v>26.747325</v>
+        <v>27.6389025</v>
       </c>
       <c r="N32">
-        <v>214.727675</v>
+        <v>213.8360975</v>
       </c>
       <c r="O32">
-        <v>75.15468625</v>
+        <v>74.84263412499999</v>
       </c>
       <c r="P32">
-        <v>139.57298875</v>
+        <v>138.993463375</v>
       </c>
       <c r="Q32">
-        <v>217.97298875</v>
+        <v>217.393463375</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1302034054880974</v>
+        <v>0.1310917904539668</v>
       </c>
       <c r="T32">
-        <v>1.228172392273551</v>
+        <v>1.24109947599111</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.028005604298748</v>
+        <v>8.736779617063304</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1012335854132371</v>
+        <v>0.100892286984806</v>
       </c>
       <c r="C33">
-        <v>1112.302459359191</v>
+        <v>1104.419024032416</v>
       </c>
       <c r="D33">
-        <v>1417.517459359191</v>
+        <v>1426.299024032416</v>
       </c>
       <c r="E33">
-        <v>-532.6849999999999</v>
+        <v>-516.02</v>
       </c>
       <c r="F33">
-        <v>516.615</v>
+        <v>533.28</v>
       </c>
       <c r="G33">
         <v>211.4</v>
@@ -3993,28 +3993,28 @@
         <v>241.475</v>
       </c>
       <c r="M33">
-        <v>27.6389025</v>
+        <v>28.53048</v>
       </c>
       <c r="N33">
-        <v>213.8360975</v>
+        <v>212.94452</v>
       </c>
       <c r="O33">
-        <v>74.84263412499999</v>
+        <v>74.530582</v>
       </c>
       <c r="P33">
-        <v>138.993463375</v>
+        <v>138.413938</v>
       </c>
       <c r="Q33">
-        <v>217.393463375</v>
+        <v>216.813938</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1310917904539668</v>
+        <v>0.1320063043894206</v>
       </c>
       <c r="T33">
-        <v>1.24109947599111</v>
+        <v>1.254406768053302</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.736779617063304</v>
+        <v>8.463755254030076</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.100892286984806</v>
+        <v>0.1005509885563749</v>
       </c>
       <c r="C34">
-        <v>1104.419024032416</v>
+        <v>1096.645071083994</v>
       </c>
       <c r="D34">
-        <v>1426.299024032416</v>
+        <v>1435.190071083993</v>
       </c>
       <c r="E34">
-        <v>-516.02</v>
+        <v>-499.3549999999999</v>
       </c>
       <c r="F34">
-        <v>533.28</v>
+        <v>549.9450000000001</v>
       </c>
       <c r="G34">
         <v>211.4</v>
@@ -4075,28 +4075,28 @@
         <v>241.475</v>
       </c>
       <c r="M34">
-        <v>28.53048</v>
+        <v>29.4220575</v>
       </c>
       <c r="N34">
-        <v>212.94452</v>
+        <v>212.0529425</v>
       </c>
       <c r="O34">
-        <v>74.530582</v>
+        <v>74.218529875</v>
       </c>
       <c r="P34">
-        <v>138.413938</v>
+        <v>137.834412625</v>
       </c>
       <c r="Q34">
-        <v>216.813938</v>
+        <v>216.234412625</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1320063043894206</v>
+        <v>0.1329481172483207</v>
       </c>
       <c r="T34">
-        <v>1.254406768053302</v>
+        <v>1.268111292714366</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.463755254030076</v>
+        <v>8.20727782208977</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1005509885563749</v>
+        <v>0.1002096901279438</v>
       </c>
       <c r="C35">
-        <v>1096.645071083994</v>
+        <v>1088.982660780958</v>
       </c>
       <c r="D35">
-        <v>1435.190071083993</v>
+        <v>1444.192660780958</v>
       </c>
       <c r="E35">
-        <v>-499.3549999999999</v>
+        <v>-482.6899999999999</v>
       </c>
       <c r="F35">
-        <v>549.9450000000001</v>
+        <v>566.61</v>
       </c>
       <c r="G35">
         <v>211.4</v>
@@ -4157,28 +4157,28 @@
         <v>241.475</v>
       </c>
       <c r="M35">
-        <v>29.4220575</v>
+        <v>30.313635</v>
       </c>
       <c r="N35">
-        <v>212.0529425</v>
+        <v>211.161365</v>
       </c>
       <c r="O35">
-        <v>74.218529875</v>
+        <v>73.90647774999999</v>
       </c>
       <c r="P35">
-        <v>137.834412625</v>
+        <v>137.25488725</v>
       </c>
       <c r="Q35">
-        <v>216.234412625</v>
+        <v>215.65488725</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1329481172483207</v>
+        <v>0.1339184698908239</v>
       </c>
       <c r="T35">
-        <v>1.268111292714366</v>
+        <v>1.282231106001522</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.20727782208977</v>
+        <v>7.965887297910659</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1002096901279438</v>
+        <v>0.09986839169951267</v>
       </c>
       <c r="C36">
-        <v>1088.982660780958</v>
+        <v>1081.433905410826</v>
       </c>
       <c r="D36">
-        <v>1444.192660780958</v>
+        <v>1453.308905410826</v>
       </c>
       <c r="E36">
-        <v>-482.6899999999999</v>
+        <v>-466.0249999999999</v>
       </c>
       <c r="F36">
-        <v>566.61</v>
+        <v>583.2750000000001</v>
       </c>
       <c r="G36">
         <v>211.4</v>
@@ -4239,28 +4239,28 @@
         <v>241.475</v>
       </c>
       <c r="M36">
-        <v>30.313635</v>
+        <v>31.20521250000001</v>
       </c>
       <c r="N36">
-        <v>211.161365</v>
+        <v>210.2697875</v>
       </c>
       <c r="O36">
-        <v>73.90647774999999</v>
+        <v>73.59442562499999</v>
       </c>
       <c r="P36">
-        <v>137.25488725</v>
+        <v>136.675361875</v>
       </c>
       <c r="Q36">
-        <v>215.65488725</v>
+        <v>215.075361875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1339184698908239</v>
+        <v>0.1349186795377118</v>
       </c>
       <c r="T36">
-        <v>1.282231106001522</v>
+        <v>1.29678537508213</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.965887297910659</v>
+        <v>7.738290517970353</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09986839169951267</v>
+        <v>0.09971429327108157</v>
       </c>
       <c r="C37">
-        <v>1081.433905410826</v>
+        <v>1068.922768973921</v>
       </c>
       <c r="D37">
-        <v>1453.308905410826</v>
+        <v>1457.462768973921</v>
       </c>
       <c r="E37">
-        <v>-466.0249999999999</v>
+        <v>-449.3599999999999</v>
       </c>
       <c r="F37">
-        <v>583.2750000000001</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="G37">
         <v>211.4</v>
@@ -4321,45 +4321,45 @@
         <v>241.475</v>
       </c>
       <c r="M37">
-        <v>31.20521250000001</v>
+        <v>32.576742</v>
       </c>
       <c r="N37">
-        <v>210.2697875</v>
+        <v>208.898258</v>
       </c>
       <c r="O37">
-        <v>73.59442562499999</v>
+        <v>73.1143903</v>
       </c>
       <c r="P37">
-        <v>136.675361875</v>
+        <v>135.7838677</v>
       </c>
       <c r="Q37">
-        <v>215.075361875</v>
+        <v>214.1838677</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1349186795377118</v>
+        <v>0.135950145736065</v>
       </c>
       <c r="T37">
-        <v>1.29678537508213</v>
+        <v>1.311794465071506</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.738290517970353</v>
+        <v>7.412496928023065</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0997142932710816</v>
+        <v>0.09937819484265048</v>
       </c>
       <c r="C38">
-        <v>1068.92276897392</v>
+        <v>1061.400498541193</v>
       </c>
       <c r="D38">
-        <v>1457.46276897392</v>
+        <v>1466.605498541193</v>
       </c>
       <c r="E38">
-        <v>-449.36</v>
+        <v>-432.6949999999999</v>
       </c>
       <c r="F38">
-        <v>599.9399999999999</v>
+        <v>616.605</v>
       </c>
       <c r="G38">
         <v>211.4</v>
@@ -4403,28 +4403,28 @@
         <v>241.475</v>
       </c>
       <c r="M38">
-        <v>32.576742</v>
+        <v>33.4816515</v>
       </c>
       <c r="N38">
-        <v>208.898258</v>
+        <v>207.9933485</v>
       </c>
       <c r="O38">
-        <v>73.1143903</v>
+        <v>72.797671975</v>
       </c>
       <c r="P38">
-        <v>135.7838677</v>
+        <v>135.195676525</v>
       </c>
       <c r="Q38">
-        <v>214.1838677</v>
+        <v>213.595676525</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.135950145736065</v>
+        <v>0.137014356893096</v>
       </c>
       <c r="T38">
-        <v>1.311794465071506</v>
+        <v>1.327280034108165</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.412496928023067</v>
+        <v>7.212159173211632</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09937819484265048</v>
+        <v>0.09904209641421936</v>
       </c>
       <c r="C39">
-        <v>1061.400498541193</v>
+        <v>1053.993657711959</v>
       </c>
       <c r="D39">
-        <v>1466.605498541193</v>
+        <v>1475.863657711959</v>
       </c>
       <c r="E39">
-        <v>-432.6949999999999</v>
+        <v>-416.03</v>
       </c>
       <c r="F39">
-        <v>616.605</v>
+        <v>633.27</v>
       </c>
       <c r="G39">
         <v>211.4</v>
@@ -4485,28 +4485,28 @@
         <v>241.475</v>
       </c>
       <c r="M39">
-        <v>33.4816515</v>
+        <v>34.386561</v>
       </c>
       <c r="N39">
-        <v>207.9933485</v>
+        <v>207.088439</v>
       </c>
       <c r="O39">
-        <v>72.797671975</v>
+        <v>72.48095364999999</v>
       </c>
       <c r="P39">
-        <v>135.195676525</v>
+        <v>134.60748535</v>
       </c>
       <c r="Q39">
-        <v>213.595676525</v>
+        <v>213.00748535</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.137014356893096</v>
+        <v>0.1381128974422893</v>
       </c>
       <c r="T39">
-        <v>1.327280034108165</v>
+        <v>1.343265137629876</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.212159173211632</v>
+        <v>7.022365510758694</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09904209641421936</v>
+        <v>0.09870599798578827</v>
       </c>
       <c r="C40">
-        <v>1053.993657711959</v>
+        <v>1046.704446371476</v>
       </c>
       <c r="D40">
-        <v>1475.863657711959</v>
+        <v>1485.239446371475</v>
       </c>
       <c r="E40">
-        <v>-416.03</v>
+        <v>-399.3649999999999</v>
       </c>
       <c r="F40">
-        <v>633.27</v>
+        <v>649.9350000000001</v>
       </c>
       <c r="G40">
         <v>211.4</v>
@@ -4567,28 +4567,28 @@
         <v>241.475</v>
       </c>
       <c r="M40">
-        <v>34.386561</v>
+        <v>35.2914705</v>
       </c>
       <c r="N40">
-        <v>207.088439</v>
+        <v>206.1835295</v>
       </c>
       <c r="O40">
-        <v>72.48095364999999</v>
+        <v>72.16423532499999</v>
       </c>
       <c r="P40">
-        <v>134.60748535</v>
+        <v>134.019294175</v>
       </c>
       <c r="Q40">
-        <v>213.00748535</v>
+        <v>212.419294175</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1381128974422893</v>
+        <v>0.139247455714407</v>
       </c>
       <c r="T40">
-        <v>1.343265137629876</v>
+        <v>1.359774342906398</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.022365510758694</v>
+        <v>6.842304856636676</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09870599798578827</v>
+        <v>0.09836989955735716</v>
       </c>
       <c r="C41">
-        <v>1046.704446371476</v>
+        <v>1039.535120663657</v>
       </c>
       <c r="D41">
-        <v>1485.239446371475</v>
+        <v>1494.735120663657</v>
       </c>
       <c r="E41">
-        <v>-399.3649999999999</v>
+        <v>-382.6999999999999</v>
       </c>
       <c r="F41">
-        <v>649.9350000000001</v>
+        <v>666.6</v>
       </c>
       <c r="G41">
         <v>211.4</v>
@@ -4649,28 +4649,28 @@
         <v>241.475</v>
       </c>
       <c r="M41">
-        <v>35.2914705</v>
+        <v>36.19638</v>
       </c>
       <c r="N41">
-        <v>206.1835295</v>
+        <v>205.27862</v>
       </c>
       <c r="O41">
-        <v>72.16423532499999</v>
+        <v>71.847517</v>
       </c>
       <c r="P41">
-        <v>134.019294175</v>
+        <v>133.431103</v>
       </c>
       <c r="Q41">
-        <v>212.419294175</v>
+        <v>211.831103</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.139247455714407</v>
+        <v>0.1404198325955953</v>
       </c>
       <c r="T41">
-        <v>1.359774342906398</v>
+        <v>1.376833855025471</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.842304856636676</v>
+        <v>6.671247235220759</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09836989955735716</v>
+        <v>0.09803380112892605</v>
       </c>
       <c r="C42">
-        <v>1039.535120663657</v>
+        <v>1032.487994801054</v>
       </c>
       <c r="D42">
-        <v>1494.735120663657</v>
+        <v>1504.352994801054</v>
       </c>
       <c r="E42">
-        <v>-382.6999999999999</v>
+        <v>-366.0349999999999</v>
       </c>
       <c r="F42">
-        <v>666.6</v>
+        <v>683.2650000000001</v>
       </c>
       <c r="G42">
         <v>211.4</v>
@@ -4731,28 +4731,28 @@
         <v>241.475</v>
       </c>
       <c r="M42">
-        <v>36.19638</v>
+        <v>37.10128950000001</v>
       </c>
       <c r="N42">
-        <v>205.27862</v>
+        <v>204.3737105</v>
       </c>
       <c r="O42">
-        <v>71.847517</v>
+        <v>71.53079867499999</v>
       </c>
       <c r="P42">
-        <v>133.431103</v>
+        <v>132.842911825</v>
       </c>
       <c r="Q42">
-        <v>211.831103</v>
+        <v>211.242911825</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1404198325955953</v>
+        <v>0.1416319510659764</v>
       </c>
       <c r="T42">
-        <v>1.376833855025471</v>
+        <v>1.394471655690953</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.671247235220759</v>
+        <v>6.508533888020252</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09803380112892605</v>
+        <v>0.09769770270049494</v>
       </c>
       <c r="C43">
-        <v>1032.487994801054</v>
+        <v>1025.565442945169</v>
       </c>
       <c r="D43">
-        <v>1504.352994801054</v>
+        <v>1514.095442945169</v>
       </c>
       <c r="E43">
-        <v>-366.0349999999999</v>
+        <v>-349.3699999999999</v>
       </c>
       <c r="F43">
-        <v>683.2650000000001</v>
+        <v>699.9300000000001</v>
       </c>
       <c r="G43">
         <v>211.4</v>
@@ -4813,28 +4813,28 @@
         <v>241.475</v>
       </c>
       <c r="M43">
-        <v>37.10128950000001</v>
+        <v>38.006199</v>
       </c>
       <c r="N43">
-        <v>204.3737105</v>
+        <v>203.468801</v>
       </c>
       <c r="O43">
-        <v>71.53079867499999</v>
+        <v>71.21408034999999</v>
       </c>
       <c r="P43">
-        <v>132.842911825</v>
+        <v>132.25472065</v>
       </c>
       <c r="Q43">
-        <v>211.242911825</v>
+        <v>210.65472065</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1416319510659764</v>
+        <v>0.1428858667249913</v>
       </c>
       <c r="T43">
-        <v>1.394471655690953</v>
+        <v>1.412717656379383</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.508533888020252</v>
+        <v>6.353568795448342</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09769770270049496</v>
+        <v>0.09736160427206386</v>
       </c>
       <c r="C44">
-        <v>1025.565442945168</v>
+        <v>1018.769901160305</v>
       </c>
       <c r="D44">
-        <v>1514.095442945168</v>
+        <v>1523.964901160305</v>
       </c>
       <c r="E44">
-        <v>-349.37</v>
+        <v>-332.7049999999999</v>
       </c>
       <c r="F44">
-        <v>699.9299999999999</v>
+        <v>716.595</v>
       </c>
       <c r="G44">
         <v>211.4</v>
@@ -4895,28 +4895,28 @@
         <v>241.475</v>
       </c>
       <c r="M44">
-        <v>38.006199</v>
+        <v>38.9111085</v>
       </c>
       <c r="N44">
-        <v>203.468801</v>
+        <v>202.5638915</v>
       </c>
       <c r="O44">
-        <v>71.21408034999999</v>
+        <v>70.89736202499999</v>
       </c>
       <c r="P44">
-        <v>132.25472065</v>
+        <v>131.666529475</v>
       </c>
       <c r="Q44">
-        <v>210.65472065</v>
+        <v>210.066529475</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1428858667249913</v>
+        <v>0.1441837794246734</v>
       </c>
       <c r="T44">
-        <v>1.412717656379383</v>
+        <v>1.431603867618284</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.353568795448343</v>
+        <v>6.205811381600705</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09736160427206386</v>
+        <v>0.09731150584363277</v>
       </c>
       <c r="C45">
-        <v>1018.769901160305</v>
+        <v>1003.587060248491</v>
       </c>
       <c r="D45">
-        <v>1523.964901160305</v>
+        <v>1525.447060248491</v>
       </c>
       <c r="E45">
-        <v>-332.7049999999999</v>
+        <v>-316.04</v>
       </c>
       <c r="F45">
-        <v>716.595</v>
+        <v>733.26</v>
       </c>
       <c r="G45">
         <v>211.4</v>
@@ -4977,45 +4977,45 @@
         <v>241.475</v>
       </c>
       <c r="M45">
-        <v>38.9111085</v>
+        <v>40.549278</v>
       </c>
       <c r="N45">
-        <v>202.5638915</v>
+        <v>200.925722</v>
       </c>
       <c r="O45">
-        <v>70.89736202499999</v>
+        <v>70.32400269999999</v>
       </c>
       <c r="P45">
-        <v>131.666529475</v>
+        <v>130.6017193</v>
       </c>
       <c r="Q45">
-        <v>210.066529475</v>
+        <v>209.0017193</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1441837794246734</v>
+        <v>0.1455280461493442</v>
       </c>
       <c r="T45">
-        <v>1.431603867618284</v>
+        <v>1.451164586401431</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.35</v>
       </c>
       <c r="W45">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.205811381600705</v>
+        <v>5.955099866389729</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09731150584363277</v>
+        <v>0.09698190741520164</v>
       </c>
       <c r="C46">
-        <v>1003.587060248491</v>
+        <v>996.7455502101692</v>
       </c>
       <c r="D46">
-        <v>1525.447060248491</v>
+        <v>1535.270550210169</v>
       </c>
       <c r="E46">
-        <v>-316.04</v>
+        <v>-299.3749999999999</v>
       </c>
       <c r="F46">
-        <v>733.26</v>
+        <v>749.9250000000001</v>
       </c>
       <c r="G46">
         <v>211.4</v>
@@ -5059,28 +5059,28 @@
         <v>241.475</v>
       </c>
       <c r="M46">
-        <v>40.549278</v>
+        <v>41.47085250000001</v>
       </c>
       <c r="N46">
-        <v>200.925722</v>
+        <v>200.0041475</v>
       </c>
       <c r="O46">
-        <v>70.32400269999999</v>
+        <v>70.00145162499999</v>
       </c>
       <c r="P46">
-        <v>130.6017193</v>
+        <v>130.002695875</v>
       </c>
       <c r="Q46">
-        <v>209.0017193</v>
+        <v>208.402695875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1455280461493442</v>
+        <v>0.1469211953003666</v>
       </c>
       <c r="T46">
-        <v>1.451164586401431</v>
+        <v>1.47143660404942</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.955099866389729</v>
+        <v>5.82276431380329</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09698190741520164</v>
+        <v>0.09665230898677055</v>
       </c>
       <c r="C47">
-        <v>996.7455502101692</v>
+        <v>990.0313817583977</v>
       </c>
       <c r="D47">
-        <v>1535.270550210169</v>
+        <v>1545.221381758398</v>
       </c>
       <c r="E47">
-        <v>-299.3749999999999</v>
+        <v>-282.7099999999999</v>
       </c>
       <c r="F47">
-        <v>749.9250000000001</v>
+        <v>766.59</v>
       </c>
       <c r="G47">
         <v>211.4</v>
@@ -5141,28 +5141,28 @@
         <v>241.475</v>
       </c>
       <c r="M47">
-        <v>41.47085250000001</v>
+        <v>42.392427</v>
       </c>
       <c r="N47">
-        <v>200.0041475</v>
+        <v>199.082573</v>
       </c>
       <c r="O47">
-        <v>70.00145162499999</v>
+        <v>69.67890054999999</v>
       </c>
       <c r="P47">
-        <v>130.002695875</v>
+        <v>129.40367245</v>
       </c>
       <c r="Q47">
-        <v>208.402695875</v>
+        <v>207.80367245</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1469211953003666</v>
+        <v>0.1483659425680936</v>
       </c>
       <c r="T47">
-        <v>1.47143660404942</v>
+        <v>1.492459437165853</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.82276431380329</v>
+        <v>5.696182480894524</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09665230898677055</v>
+        <v>0.09632271055833944</v>
       </c>
       <c r="C48">
-        <v>990.0313817583977</v>
+        <v>983.4470471339743</v>
       </c>
       <c r="D48">
-        <v>1545.221381758398</v>
+        <v>1555.302047133974</v>
       </c>
       <c r="E48">
-        <v>-282.7099999999999</v>
+        <v>-266.045</v>
       </c>
       <c r="F48">
-        <v>766.59</v>
+        <v>783.255</v>
       </c>
       <c r="G48">
         <v>211.4</v>
@@ -5223,28 +5223,28 @@
         <v>241.475</v>
       </c>
       <c r="M48">
-        <v>42.392427</v>
+        <v>43.3140015</v>
       </c>
       <c r="N48">
-        <v>199.082573</v>
+        <v>198.1609985</v>
       </c>
       <c r="O48">
-        <v>69.67890054999999</v>
+        <v>69.356349475</v>
       </c>
       <c r="P48">
-        <v>129.40367245</v>
+        <v>128.804649025</v>
       </c>
       <c r="Q48">
-        <v>207.80367245</v>
+        <v>207.204649025</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1483659425680936</v>
+        <v>0.1498652086006404</v>
       </c>
       <c r="T48">
-        <v>1.492459437165853</v>
+        <v>1.51427558473951</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.696182480894524</v>
+        <v>5.574987108960598</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09632271055833944</v>
+        <v>0.09599311212990833</v>
       </c>
       <c r="C49">
-        <v>983.4470471339743</v>
+        <v>976.9951040399551</v>
       </c>
       <c r="D49">
-        <v>1555.302047133974</v>
+        <v>1565.515104039955</v>
       </c>
       <c r="E49">
-        <v>-266.045</v>
+        <v>-249.3799999999999</v>
       </c>
       <c r="F49">
-        <v>783.255</v>
+        <v>799.9200000000001</v>
       </c>
       <c r="G49">
         <v>211.4</v>
@@ -5305,28 +5305,28 @@
         <v>241.475</v>
       </c>
       <c r="M49">
-        <v>43.3140015</v>
+        <v>44.23557600000001</v>
       </c>
       <c r="N49">
-        <v>198.1609985</v>
+        <v>197.239424</v>
       </c>
       <c r="O49">
-        <v>69.356349475</v>
+        <v>69.03379839999999</v>
       </c>
       <c r="P49">
-        <v>128.804649025</v>
+        <v>128.2056256</v>
       </c>
       <c r="Q49">
-        <v>207.204649025</v>
+        <v>206.6056256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1498652086006404</v>
+        <v>0.1514221387113621</v>
       </c>
       <c r="T49">
-        <v>1.51427558473951</v>
+        <v>1.536930814912154</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.574987108960598</v>
+        <v>5.458841544190584</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09599311212990833</v>
+        <v>0.09566351370147723</v>
       </c>
       <c r="C50">
-        <v>976.9951040399552</v>
+        <v>970.6781778051907</v>
       </c>
       <c r="D50">
-        <v>1565.515104039955</v>
+        <v>1575.863177805191</v>
       </c>
       <c r="E50">
-        <v>-249.38</v>
+        <v>-232.7149999999999</v>
       </c>
       <c r="F50">
-        <v>799.92</v>
+        <v>816.585</v>
       </c>
       <c r="G50">
         <v>211.4</v>
@@ -5387,28 +5387,28 @@
         <v>241.475</v>
       </c>
       <c r="M50">
-        <v>44.235576</v>
+        <v>45.1571505</v>
       </c>
       <c r="N50">
-        <v>197.239424</v>
+        <v>196.3178495</v>
       </c>
       <c r="O50">
-        <v>69.03379839999999</v>
+        <v>68.71124732499999</v>
       </c>
       <c r="P50">
-        <v>128.2056256</v>
+        <v>127.606602175</v>
       </c>
       <c r="Q50">
-        <v>206.6056256</v>
+        <v>206.006602175</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1514221387113621</v>
+        <v>0.1530401249048573</v>
       </c>
       <c r="T50">
-        <v>1.536930814912154</v>
+        <v>1.560474485483725</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.458841544190585</v>
+        <v>5.347436614717308</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09566351370147723</v>
+        <v>0.09533391527304612</v>
       </c>
       <c r="C51">
-        <v>970.6781778051907</v>
+        <v>964.498963634232</v>
       </c>
       <c r="D51">
-        <v>1575.863177805191</v>
+        <v>1586.348963634232</v>
       </c>
       <c r="E51">
-        <v>-232.7149999999999</v>
+        <v>-216.05</v>
       </c>
       <c r="F51">
-        <v>816.585</v>
+        <v>833.25</v>
       </c>
       <c r="G51">
         <v>211.4</v>
@@ -5469,28 +5469,28 @@
         <v>241.475</v>
       </c>
       <c r="M51">
-        <v>45.1571505</v>
+        <v>46.078725</v>
       </c>
       <c r="N51">
-        <v>196.3178495</v>
+        <v>195.396275</v>
       </c>
       <c r="O51">
-        <v>68.71124732499999</v>
+        <v>68.38869625</v>
       </c>
       <c r="P51">
-        <v>127.606602175</v>
+        <v>127.00757875</v>
       </c>
       <c r="Q51">
-        <v>206.006602175</v>
+        <v>205.40757875</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1530401249048573</v>
+        <v>0.1547228305460922</v>
       </c>
       <c r="T51">
-        <v>1.560474485483725</v>
+        <v>1.584959902878158</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.347436614717308</v>
+        <v>5.240487882422962</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09533391527304612</v>
+        <v>0.09500431684461501</v>
       </c>
       <c r="C52">
-        <v>964.498963634232</v>
+        <v>958.4602289476666</v>
       </c>
       <c r="D52">
-        <v>1586.348963634232</v>
+        <v>1596.975228947666</v>
       </c>
       <c r="E52">
-        <v>-216.05</v>
+        <v>-199.385</v>
       </c>
       <c r="F52">
-        <v>833.25</v>
+        <v>849.915</v>
       </c>
       <c r="G52">
         <v>211.4</v>
@@ -5551,28 +5551,28 @@
         <v>241.475</v>
       </c>
       <c r="M52">
-        <v>46.078725</v>
+        <v>47.0002995</v>
       </c>
       <c r="N52">
-        <v>195.396275</v>
+        <v>194.4747005</v>
       </c>
       <c r="O52">
-        <v>68.38869625</v>
+        <v>68.06614517499999</v>
       </c>
       <c r="P52">
-        <v>127.00757875</v>
+        <v>126.408555325</v>
       </c>
       <c r="Q52">
-        <v>205.40757875</v>
+        <v>204.808555325</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1547228305460922</v>
+        <v>0.1564742180502347</v>
       </c>
       <c r="T52">
-        <v>1.584959902878158</v>
+        <v>1.610444725064202</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.240487882422962</v>
+        <v>5.137733218061728</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09500431684461501</v>
+        <v>0.09467471841618391</v>
       </c>
       <c r="C53">
-        <v>958.4602289476666</v>
+        <v>952.5648158171479</v>
       </c>
       <c r="D53">
-        <v>1596.975228947666</v>
+        <v>1607.744815817148</v>
       </c>
       <c r="E53">
-        <v>-199.385</v>
+        <v>-182.7199999999999</v>
       </c>
       <c r="F53">
-        <v>849.915</v>
+        <v>866.58</v>
       </c>
       <c r="G53">
         <v>211.4</v>
@@ -5633,28 +5633,28 @@
         <v>241.475</v>
       </c>
       <c r="M53">
-        <v>47.0002995</v>
+        <v>47.921874</v>
       </c>
       <c r="N53">
-        <v>194.4747005</v>
+        <v>193.553126</v>
       </c>
       <c r="O53">
-        <v>68.06614517499999</v>
+        <v>67.7435941</v>
       </c>
       <c r="P53">
-        <v>126.408555325</v>
+        <v>125.8095319</v>
       </c>
       <c r="Q53">
-        <v>204.808555325</v>
+        <v>204.2095319</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1564742180502347</v>
+        <v>0.1582985800337165</v>
       </c>
       <c r="T53">
-        <v>1.610444725064202</v>
+        <v>1.63699141484133</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.137733218061728</v>
+        <v>5.038930656175925</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09467471841618391</v>
+        <v>0.0943451199877528</v>
       </c>
       <c r="C54">
-        <v>952.5648158171479</v>
+        <v>946.8156434996273</v>
       </c>
       <c r="D54">
-        <v>1607.744815817148</v>
+        <v>1618.660643499627</v>
       </c>
       <c r="E54">
-        <v>-182.7199999999999</v>
+        <v>-166.0549999999999</v>
       </c>
       <c r="F54">
-        <v>866.58</v>
+        <v>883.245</v>
       </c>
       <c r="G54">
         <v>211.4</v>
@@ -5715,28 +5715,28 @@
         <v>241.475</v>
       </c>
       <c r="M54">
-        <v>47.921874</v>
+        <v>48.8434485</v>
       </c>
       <c r="N54">
-        <v>193.553126</v>
+        <v>192.6315515</v>
       </c>
       <c r="O54">
-        <v>67.7435941</v>
+        <v>67.42104302499999</v>
       </c>
       <c r="P54">
-        <v>125.8095319</v>
+        <v>125.210508475</v>
       </c>
       <c r="Q54">
-        <v>204.2095319</v>
+        <v>203.610508475</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1582985800337165</v>
+        <v>0.1602005744420272</v>
       </c>
       <c r="T54">
-        <v>1.63699141484133</v>
+        <v>1.664667750991954</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.038930656175925</v>
+        <v>4.94385649285185</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0943451199877528</v>
+        <v>0.0940155215593217</v>
       </c>
       <c r="C55">
-        <v>946.8156434996273</v>
+        <v>941.2157110755188</v>
       </c>
       <c r="D55">
-        <v>1618.660643499627</v>
+        <v>1629.725711075519</v>
       </c>
       <c r="E55">
-        <v>-166.0549999999999</v>
+        <v>-149.3899999999999</v>
       </c>
       <c r="F55">
-        <v>883.245</v>
+        <v>899.9100000000001</v>
       </c>
       <c r="G55">
         <v>211.4</v>
@@ -5797,28 +5797,28 @@
         <v>241.475</v>
       </c>
       <c r="M55">
-        <v>48.8434485</v>
+        <v>49.76502300000001</v>
       </c>
       <c r="N55">
-        <v>192.6315515</v>
+        <v>191.709977</v>
       </c>
       <c r="O55">
-        <v>67.42104302499999</v>
+        <v>67.09849195</v>
       </c>
       <c r="P55">
-        <v>125.210508475</v>
+        <v>124.61148505</v>
       </c>
       <c r="Q55">
-        <v>203.610508475</v>
+        <v>203.01148505</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1602005744420272</v>
+        <v>0.162185264259395</v>
       </c>
       <c r="T55">
-        <v>1.664667750991954</v>
+        <v>1.693547406105648</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.94385649285185</v>
+        <v>4.852303594836075</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0940155215593217</v>
+        <v>0.09368592313089059</v>
       </c>
       <c r="C56">
-        <v>941.2157110755188</v>
+        <v>935.7681001958247</v>
       </c>
       <c r="D56">
-        <v>1629.725711075519</v>
+        <v>1640.943100195825</v>
       </c>
       <c r="E56">
-        <v>-149.3899999999999</v>
+        <v>-132.7249999999999</v>
       </c>
       <c r="F56">
-        <v>899.9100000000001</v>
+        <v>916.575</v>
       </c>
       <c r="G56">
         <v>211.4</v>
@@ -5879,28 +5879,28 @@
         <v>241.475</v>
       </c>
       <c r="M56">
-        <v>49.76502300000001</v>
+        <v>50.6865975</v>
       </c>
       <c r="N56">
-        <v>191.709977</v>
+        <v>190.7884025</v>
       </c>
       <c r="O56">
-        <v>67.09849195</v>
+        <v>66.77594087499999</v>
       </c>
       <c r="P56">
-        <v>124.61148505</v>
+        <v>124.012461625</v>
       </c>
       <c r="Q56">
-        <v>203.01148505</v>
+        <v>202.412461625</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.162185264259395</v>
+        <v>0.1642581625130902</v>
       </c>
       <c r="T56">
-        <v>1.693547406105648</v>
+        <v>1.723710601446617</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.852303594836075</v>
+        <v>4.764079893111782</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09368592313089059</v>
+        <v>0.09335632470245948</v>
       </c>
       <c r="C57">
-        <v>935.7681001958247</v>
+        <v>930.4759779434916</v>
       </c>
       <c r="D57">
-        <v>1640.943100195825</v>
+        <v>1652.315977943492</v>
       </c>
       <c r="E57">
-        <v>-132.7249999999999</v>
+        <v>-116.0599999999998</v>
       </c>
       <c r="F57">
-        <v>916.575</v>
+        <v>933.2400000000001</v>
       </c>
       <c r="G57">
         <v>211.4</v>
@@ -5961,28 +5961,28 @@
         <v>241.475</v>
       </c>
       <c r="M57">
-        <v>50.6865975</v>
+        <v>51.60817200000001</v>
       </c>
       <c r="N57">
-        <v>190.7884025</v>
+        <v>189.866828</v>
       </c>
       <c r="O57">
-        <v>66.77594087499999</v>
+        <v>66.4533898</v>
       </c>
       <c r="P57">
-        <v>124.012461625</v>
+        <v>123.4134382</v>
       </c>
       <c r="Q57">
-        <v>202.412461625</v>
+        <v>201.8134382</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1642581625130902</v>
+        <v>0.1664252834146807</v>
       </c>
       <c r="T57">
-        <v>1.723710601446617</v>
+        <v>1.755244851121267</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.764079893111782</v>
+        <v>4.679007037877644</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09335632470245948</v>
+        <v>0.09302672627402839</v>
       </c>
       <c r="C58">
-        <v>930.4759779434916</v>
+        <v>925.3425998145859</v>
       </c>
       <c r="D58">
-        <v>1652.315977943492</v>
+        <v>1663.847599814586</v>
       </c>
       <c r="E58">
-        <v>-116.0599999999998</v>
+        <v>-99.39499999999987</v>
       </c>
       <c r="F58">
-        <v>933.2400000000001</v>
+        <v>949.9050000000001</v>
       </c>
       <c r="G58">
         <v>211.4</v>
@@ -6043,28 +6043,28 @@
         <v>241.475</v>
       </c>
       <c r="M58">
-        <v>51.60817200000001</v>
+        <v>52.52974650000001</v>
       </c>
       <c r="N58">
-        <v>189.866828</v>
+        <v>188.9452535</v>
       </c>
       <c r="O58">
-        <v>66.4533898</v>
+        <v>66.13083872499999</v>
       </c>
       <c r="P58">
-        <v>123.4134382</v>
+        <v>122.814414775</v>
       </c>
       <c r="Q58">
-        <v>201.8134382</v>
+        <v>201.214414775</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1664252834146807</v>
+        <v>0.1686932006372753</v>
       </c>
       <c r="T58">
-        <v>1.755244851121267</v>
+        <v>1.788245810083109</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.679007037877644</v>
+        <v>4.59691919510786</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09302672627402839</v>
+        <v>0.09269712784559729</v>
       </c>
       <c r="C59">
-        <v>925.3425998145859</v>
+        <v>920.3713128251836</v>
       </c>
       <c r="D59">
-        <v>1663.847599814586</v>
+        <v>1675.541312825184</v>
       </c>
       <c r="E59">
-        <v>-99.39499999999987</v>
+        <v>-82.72999999999979</v>
       </c>
       <c r="F59">
-        <v>949.9050000000001</v>
+        <v>966.5700000000002</v>
       </c>
       <c r="G59">
         <v>211.4</v>
@@ -6125,28 +6125,28 @@
         <v>241.475</v>
       </c>
       <c r="M59">
-        <v>52.52974650000001</v>
+        <v>53.45132100000001</v>
       </c>
       <c r="N59">
-        <v>188.9452535</v>
+        <v>188.023679</v>
       </c>
       <c r="O59">
-        <v>66.13083872499999</v>
+        <v>65.80828765</v>
       </c>
       <c r="P59">
-        <v>122.814414775</v>
+        <v>122.21539135</v>
       </c>
       <c r="Q59">
-        <v>201.214414775</v>
+        <v>200.61539135</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1686932006372753</v>
+        <v>0.1710691139180888</v>
       </c>
       <c r="T59">
-        <v>1.788245810083109</v>
+        <v>1.82281824328123</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.59691919510786</v>
+        <v>4.517661967606001</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09269712784559728</v>
+        <v>0.09332627941716617</v>
       </c>
       <c r="C60">
-        <v>920.3713128251843</v>
+        <v>881.5255432989291</v>
       </c>
       <c r="D60">
-        <v>1675.541312825184</v>
+        <v>1653.360543298929</v>
       </c>
       <c r="E60">
-        <v>-82.73000000000002</v>
+        <v>-66.06500000000005</v>
       </c>
       <c r="F60">
-        <v>966.5699999999999</v>
+        <v>983.2349999999999</v>
       </c>
       <c r="G60">
         <v>211.4</v>
@@ -6207,45 +6207,45 @@
         <v>241.475</v>
       </c>
       <c r="M60">
-        <v>53.451321</v>
+        <v>56.830983</v>
       </c>
       <c r="N60">
-        <v>188.023679</v>
+        <v>184.644017</v>
       </c>
       <c r="O60">
-        <v>65.80828765</v>
+        <v>64.62540594999999</v>
       </c>
       <c r="P60">
-        <v>122.21539135</v>
+        <v>120.01861105</v>
       </c>
       <c r="Q60">
-        <v>200.61539135</v>
+        <v>198.41861105</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1710691139180888</v>
+        <v>0.1735609254077224</v>
       </c>
       <c r="T60">
-        <v>1.82281824328123</v>
+        <v>1.859077136635356</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.517661967606001</v>
+        <v>4.249002696293323</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09332627941716617</v>
+        <v>0.09301293098873507</v>
       </c>
       <c r="C61">
-        <v>881.5255432989291</v>
+        <v>875.833764342891</v>
       </c>
       <c r="D61">
-        <v>1653.360543298929</v>
+        <v>1664.333764342891</v>
       </c>
       <c r="E61">
-        <v>-66.06500000000005</v>
+        <v>-49.39999999999998</v>
       </c>
       <c r="F61">
-        <v>983.2349999999999</v>
+        <v>999.9</v>
       </c>
       <c r="G61">
         <v>211.4</v>
@@ -6289,28 +6289,28 @@
         <v>241.475</v>
       </c>
       <c r="M61">
-        <v>56.830983</v>
+        <v>57.79422</v>
       </c>
       <c r="N61">
-        <v>184.644017</v>
+        <v>183.68078</v>
       </c>
       <c r="O61">
-        <v>64.62540594999999</v>
+        <v>64.28827299999999</v>
       </c>
       <c r="P61">
-        <v>120.01861105</v>
+        <v>119.392507</v>
       </c>
       <c r="Q61">
-        <v>198.41861105</v>
+        <v>197.792507</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1735609254077224</v>
+        <v>0.1761773274718376</v>
       </c>
       <c r="T61">
-        <v>1.859077136635356</v>
+        <v>1.897148974657189</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.249002696293323</v>
+        <v>4.178185984688434</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09301293098873507</v>
+        <v>0.09269958256030397</v>
       </c>
       <c r="C62">
-        <v>875.833764342891</v>
+        <v>870.2886153302871</v>
       </c>
       <c r="D62">
-        <v>1664.333764342891</v>
+        <v>1675.453615330287</v>
       </c>
       <c r="E62">
-        <v>-49.39999999999998</v>
+        <v>-32.73500000000001</v>
       </c>
       <c r="F62">
-        <v>999.9</v>
+        <v>1016.565</v>
       </c>
       <c r="G62">
         <v>211.4</v>
@@ -6371,28 +6371,28 @@
         <v>241.475</v>
       </c>
       <c r="M62">
-        <v>57.79422</v>
+        <v>58.757457</v>
       </c>
       <c r="N62">
-        <v>183.68078</v>
+        <v>182.717543</v>
       </c>
       <c r="O62">
-        <v>64.28827299999999</v>
+        <v>63.95114004999999</v>
       </c>
       <c r="P62">
-        <v>119.392507</v>
+        <v>118.76640295</v>
       </c>
       <c r="Q62">
-        <v>197.792507</v>
+        <v>197.16640295</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1761773274718376</v>
+        <v>0.1789279040007794</v>
       </c>
       <c r="T62">
-        <v>1.897148974657189</v>
+        <v>1.93717321462886</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.178185984688434</v>
+        <v>4.109691132480426</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09269958256030397</v>
+        <v>0.09238623413187287</v>
       </c>
       <c r="C63">
-        <v>870.2886153302871</v>
+        <v>864.8930550490422</v>
       </c>
       <c r="D63">
-        <v>1675.453615330287</v>
+        <v>1686.723055049042</v>
       </c>
       <c r="E63">
-        <v>-32.73500000000001</v>
+        <v>-16.06999999999994</v>
       </c>
       <c r="F63">
-        <v>1016.565</v>
+        <v>1033.23</v>
       </c>
       <c r="G63">
         <v>211.4</v>
@@ -6453,28 +6453,28 @@
         <v>241.475</v>
       </c>
       <c r="M63">
-        <v>58.757457</v>
+        <v>59.72069400000001</v>
       </c>
       <c r="N63">
-        <v>182.717543</v>
+        <v>181.754306</v>
       </c>
       <c r="O63">
-        <v>63.95114004999999</v>
+        <v>63.61400709999999</v>
       </c>
       <c r="P63">
-        <v>118.76640295</v>
+        <v>118.1402989</v>
       </c>
       <c r="Q63">
-        <v>197.16640295</v>
+        <v>196.5402989</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1789279040007794</v>
+        <v>0.1818232477154549</v>
       </c>
       <c r="T63">
-        <v>1.93717321462886</v>
+        <v>1.979303993546409</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.109691132480426</v>
+        <v>4.043405791633968</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09238623413187287</v>
+        <v>0.09350613570344175</v>
       </c>
       <c r="C64">
-        <v>864.8930550490422</v>
+        <v>808.6322300613851</v>
       </c>
       <c r="D64">
-        <v>1686.723055049042</v>
+        <v>1647.127230061385</v>
       </c>
       <c r="E64">
-        <v>-16.06999999999994</v>
+        <v>0.5950000000000273</v>
       </c>
       <c r="F64">
-        <v>1033.23</v>
+        <v>1049.895</v>
       </c>
       <c r="G64">
         <v>211.4</v>
@@ -6535,45 +6535,45 @@
         <v>241.475</v>
       </c>
       <c r="M64">
-        <v>59.72069400000001</v>
+        <v>64.3585635</v>
       </c>
       <c r="N64">
-        <v>181.754306</v>
+        <v>177.1164365</v>
       </c>
       <c r="O64">
-        <v>63.61400709999999</v>
+        <v>61.99075277499999</v>
       </c>
       <c r="P64">
-        <v>118.1402989</v>
+        <v>115.125683725</v>
       </c>
       <c r="Q64">
-        <v>196.5402989</v>
+        <v>193.525683725</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1818232477154549</v>
+        <v>0.1848750964957885</v>
       </c>
       <c r="T64">
-        <v>1.979303993546409</v>
+        <v>2.023712111864905</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.043405791633968</v>
+        <v>3.752025944457259</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09350613570344175</v>
+        <v>0.09321553727501065</v>
       </c>
       <c r="C65">
-        <v>808.6322300613851</v>
+        <v>802.0620768561337</v>
       </c>
       <c r="D65">
-        <v>1647.127230061385</v>
+        <v>1657.222076856134</v>
       </c>
       <c r="E65">
-        <v>0.5950000000000273</v>
+        <v>17.25999999999999</v>
       </c>
       <c r="F65">
-        <v>1049.895</v>
+        <v>1066.56</v>
       </c>
       <c r="G65">
         <v>211.4</v>
@@ -6617,28 +6617,28 @@
         <v>241.475</v>
       </c>
       <c r="M65">
-        <v>64.3585635</v>
+        <v>65.380128</v>
       </c>
       <c r="N65">
-        <v>177.1164365</v>
+        <v>176.094872</v>
       </c>
       <c r="O65">
-        <v>61.99075277499999</v>
+        <v>61.6332052</v>
       </c>
       <c r="P65">
-        <v>115.125683725</v>
+        <v>114.4616668</v>
       </c>
       <c r="Q65">
-        <v>193.525683725</v>
+        <v>192.8616668</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1848750964957885</v>
+        <v>0.1880964924305852</v>
       </c>
       <c r="T65">
-        <v>2.023712111864905</v>
+        <v>2.070587347867763</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.752025944457259</v>
+        <v>3.693400539075115</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09321553727501065</v>
+        <v>0.09292493884657954</v>
       </c>
       <c r="C66">
-        <v>802.0620768561337</v>
+        <v>795.6164244644899</v>
       </c>
       <c r="D66">
-        <v>1657.222076856134</v>
+        <v>1667.44142446449</v>
       </c>
       <c r="E66">
-        <v>17.25999999999999</v>
+        <v>33.92500000000018</v>
       </c>
       <c r="F66">
-        <v>1066.56</v>
+        <v>1083.225</v>
       </c>
       <c r="G66">
         <v>211.4</v>
@@ -6699,28 +6699,28 @@
         <v>241.475</v>
       </c>
       <c r="M66">
-        <v>65.380128</v>
+        <v>66.40169250000001</v>
       </c>
       <c r="N66">
-        <v>176.094872</v>
+        <v>175.0733075</v>
       </c>
       <c r="O66">
-        <v>61.6332052</v>
+        <v>61.27565762499999</v>
       </c>
       <c r="P66">
-        <v>114.4616668</v>
+        <v>113.797649875</v>
       </c>
       <c r="Q66">
-        <v>192.8616668</v>
+        <v>192.197649875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1880964924305852</v>
+        <v>0.1915019681330844</v>
       </c>
       <c r="T66">
-        <v>2.070587347867763</v>
+        <v>2.120141168785069</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.693400539075115</v>
+        <v>3.636578992320112</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09292493884657954</v>
+        <v>0.09263434041814841</v>
       </c>
       <c r="C67">
-        <v>795.6164244644899</v>
+        <v>789.2975904000855</v>
       </c>
       <c r="D67">
-        <v>1667.44142446449</v>
+        <v>1677.787590400085</v>
       </c>
       <c r="E67">
-        <v>33.92500000000018</v>
+        <v>50.59000000000015</v>
       </c>
       <c r="F67">
-        <v>1083.225</v>
+        <v>1099.89</v>
       </c>
       <c r="G67">
         <v>211.4</v>
@@ -6781,28 +6781,28 @@
         <v>241.475</v>
       </c>
       <c r="M67">
-        <v>66.40169250000001</v>
+        <v>67.42325700000001</v>
       </c>
       <c r="N67">
-        <v>175.0733075</v>
+        <v>174.051743</v>
       </c>
       <c r="O67">
-        <v>61.27565762499999</v>
+        <v>60.91811004999999</v>
       </c>
       <c r="P67">
-        <v>113.797649875</v>
+        <v>113.13363295</v>
       </c>
       <c r="Q67">
-        <v>192.197649875</v>
+        <v>191.53363295</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1915019681330844</v>
+        <v>0.1951077659357307</v>
       </c>
       <c r="T67">
-        <v>2.120141168785069</v>
+        <v>2.17260992034457</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.636578992320112</v>
+        <v>3.581479310618293</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09263434041814841</v>
+        <v>0.09234374198971734</v>
       </c>
       <c r="C68">
-        <v>789.2975904000855</v>
+        <v>783.1079500546475</v>
       </c>
       <c r="D68">
-        <v>1677.787590400085</v>
+        <v>1688.262950054647</v>
       </c>
       <c r="E68">
-        <v>50.59000000000015</v>
+        <v>67.25500000000011</v>
       </c>
       <c r="F68">
-        <v>1099.89</v>
+        <v>1116.555</v>
       </c>
       <c r="G68">
         <v>211.4</v>
@@ -6863,28 +6863,28 @@
         <v>241.475</v>
       </c>
       <c r="M68">
-        <v>67.42325700000001</v>
+        <v>68.4448215</v>
       </c>
       <c r="N68">
-        <v>174.051743</v>
+        <v>173.0301785</v>
       </c>
       <c r="O68">
-        <v>60.91811004999999</v>
+        <v>60.56056247499999</v>
       </c>
       <c r="P68">
-        <v>113.13363295</v>
+        <v>112.469616025</v>
       </c>
       <c r="Q68">
-        <v>191.53363295</v>
+        <v>190.869616025</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1951077659357307</v>
+        <v>0.1989320969385374</v>
       </c>
       <c r="T68">
-        <v>2.17260992034457</v>
+        <v>2.228258596241011</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.581479310618293</v>
+        <v>3.528024395534437</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09234374198971734</v>
+        <v>0.09329074356128625</v>
       </c>
       <c r="C69">
-        <v>783.1079500546475</v>
+        <v>732.777701902445</v>
       </c>
       <c r="D69">
-        <v>1688.262950054647</v>
+        <v>1654.597701902445</v>
       </c>
       <c r="E69">
-        <v>67.25500000000011</v>
+        <v>83.92000000000007</v>
       </c>
       <c r="F69">
-        <v>1116.555</v>
+        <v>1133.22</v>
       </c>
       <c r="G69">
         <v>211.4</v>
@@ -6945,45 +6945,45 @@
         <v>241.475</v>
       </c>
       <c r="M69">
-        <v>68.4448215</v>
+        <v>72.639402</v>
       </c>
       <c r="N69">
-        <v>173.0301785</v>
+        <v>168.835598</v>
       </c>
       <c r="O69">
-        <v>60.56056247499999</v>
+        <v>59.09245929999999</v>
       </c>
       <c r="P69">
-        <v>112.469616025</v>
+        <v>109.7431387</v>
       </c>
       <c r="Q69">
-        <v>190.869616025</v>
+        <v>188.1431387</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1989320969385374</v>
+        <v>0.2029954486290195</v>
       </c>
       <c r="T69">
-        <v>2.228258596241011</v>
+        <v>2.287385314380979</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.528024395534437</v>
+        <v>3.324297741327771</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09329074356128625</v>
+        <v>0.09301834513285513</v>
       </c>
       <c r="C70">
-        <v>732.777701902445</v>
+        <v>725.6579287081672</v>
       </c>
       <c r="D70">
-        <v>1654.597701902445</v>
+        <v>1664.142928708167</v>
       </c>
       <c r="E70">
-        <v>83.92000000000007</v>
+        <v>100.585</v>
       </c>
       <c r="F70">
-        <v>1133.22</v>
+        <v>1149.885</v>
       </c>
       <c r="G70">
         <v>211.4</v>
@@ -7027,28 +7027,28 @@
         <v>241.475</v>
       </c>
       <c r="M70">
-        <v>72.639402</v>
+        <v>73.7076285</v>
       </c>
       <c r="N70">
-        <v>168.835598</v>
+        <v>167.7673715</v>
       </c>
       <c r="O70">
-        <v>59.09245929999999</v>
+        <v>58.71858002499999</v>
       </c>
       <c r="P70">
-        <v>109.7431387</v>
+        <v>109.048791475</v>
       </c>
       <c r="Q70">
-        <v>188.1431387</v>
+        <v>187.448791475</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2029954486290195</v>
+        <v>0.2073209520414682</v>
       </c>
       <c r="T70">
-        <v>2.287385314380979</v>
+        <v>2.350326659497719</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.324297741327771</v>
+        <v>3.276119513192586</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09301834513285513</v>
+        <v>0.09274594670442403</v>
       </c>
       <c r="C71">
-        <v>725.6579287081672</v>
+        <v>718.648925663962</v>
       </c>
       <c r="D71">
-        <v>1664.142928708167</v>
+        <v>1673.798925663962</v>
       </c>
       <c r="E71">
-        <v>100.585</v>
+        <v>117.2500000000002</v>
       </c>
       <c r="F71">
-        <v>1149.885</v>
+        <v>1166.55</v>
       </c>
       <c r="G71">
         <v>211.4</v>
@@ -7109,28 +7109,28 @@
         <v>241.475</v>
       </c>
       <c r="M71">
-        <v>73.7076285</v>
+        <v>74.77585500000002</v>
       </c>
       <c r="N71">
-        <v>167.7673715</v>
+        <v>166.699145</v>
       </c>
       <c r="O71">
-        <v>58.71858002499999</v>
+        <v>58.34470074999999</v>
       </c>
       <c r="P71">
-        <v>109.048791475</v>
+        <v>108.35444425</v>
       </c>
       <c r="Q71">
-        <v>187.448791475</v>
+        <v>186.75444425</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2073209520414682</v>
+        <v>0.2119348223480801</v>
       </c>
       <c r="T71">
-        <v>2.350326659497719</v>
+        <v>2.417464094288909</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.276119513192586</v>
+        <v>3.229317805861263</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09274594670442403</v>
+        <v>0.09247354827599294</v>
       </c>
       <c r="C72">
-        <v>718.648925663962</v>
+        <v>711.7526322162134</v>
       </c>
       <c r="D72">
-        <v>1673.798925663962</v>
+        <v>1683.567632216213</v>
       </c>
       <c r="E72">
-        <v>117.2500000000002</v>
+        <v>133.9150000000002</v>
       </c>
       <c r="F72">
-        <v>1166.55</v>
+        <v>1183.215</v>
       </c>
       <c r="G72">
         <v>211.4</v>
@@ -7191,28 +7191,28 @@
         <v>241.475</v>
       </c>
       <c r="M72">
-        <v>74.77585500000002</v>
+        <v>75.84408150000002</v>
       </c>
       <c r="N72">
-        <v>166.699145</v>
+        <v>165.6309185</v>
       </c>
       <c r="O72">
-        <v>58.34470074999999</v>
+        <v>57.97082147499999</v>
       </c>
       <c r="P72">
-        <v>108.35444425</v>
+        <v>107.660097025</v>
       </c>
       <c r="Q72">
-        <v>186.75444425</v>
+        <v>186.060097025</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2119348223480801</v>
+        <v>0.2168668906068722</v>
       </c>
       <c r="T72">
-        <v>2.417464094288909</v>
+        <v>2.489231696996733</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.229317805861263</v>
+        <v>3.183834456482935</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09247354827599293</v>
+        <v>0.09220114984756181</v>
       </c>
       <c r="C73">
-        <v>711.7526322162144</v>
+        <v>704.9710333534663</v>
       </c>
       <c r="D73">
-        <v>1683.567632216214</v>
+        <v>1693.451033353466</v>
       </c>
       <c r="E73">
-        <v>133.915</v>
+        <v>150.5799999999999</v>
       </c>
       <c r="F73">
-        <v>1183.215</v>
+        <v>1199.88</v>
       </c>
       <c r="G73">
         <v>211.4</v>
@@ -7273,28 +7273,28 @@
         <v>241.475</v>
       </c>
       <c r="M73">
-        <v>75.8440815</v>
+        <v>76.912308</v>
       </c>
       <c r="N73">
-        <v>165.6309185</v>
+        <v>164.562692</v>
       </c>
       <c r="O73">
-        <v>57.970821475</v>
+        <v>57.59694219999999</v>
       </c>
       <c r="P73">
-        <v>107.660097025</v>
+        <v>106.9657498</v>
       </c>
       <c r="Q73">
-        <v>186.060097025</v>
+        <v>185.3657498</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2168668906068721</v>
+        <v>0.2221512494555779</v>
       </c>
       <c r="T73">
-        <v>2.489231696996732</v>
+        <v>2.566125557040828</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.183834456482936</v>
+        <v>3.139614533476228</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09220114984756181</v>
+        <v>0.09192875141913071</v>
       </c>
       <c r="C74">
-        <v>704.9710333534663</v>
+        <v>698.3061609510928</v>
       </c>
       <c r="D74">
-        <v>1693.451033353466</v>
+        <v>1703.451160951093</v>
       </c>
       <c r="E74">
-        <v>150.5799999999999</v>
+        <v>167.2450000000001</v>
       </c>
       <c r="F74">
-        <v>1199.88</v>
+        <v>1216.545</v>
       </c>
       <c r="G74">
         <v>211.4</v>
@@ -7355,28 +7355,28 @@
         <v>241.475</v>
       </c>
       <c r="M74">
-        <v>76.912308</v>
+        <v>77.9805345</v>
       </c>
       <c r="N74">
-        <v>164.562692</v>
+        <v>163.4944655</v>
       </c>
       <c r="O74">
-        <v>57.59694219999999</v>
+        <v>57.22306292499999</v>
       </c>
       <c r="P74">
-        <v>106.9657498</v>
+        <v>106.271402575</v>
       </c>
       <c r="Q74">
-        <v>185.3657498</v>
+        <v>184.671402575</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2221512494555779</v>
+        <v>0.2278270422930767</v>
       </c>
       <c r="T74">
-        <v>2.566125557040828</v>
+        <v>2.648715258569672</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.139614533476228</v>
+        <v>3.096606115209431</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09192875141913071</v>
+        <v>0.0916563529906996</v>
       </c>
       <c r="C75">
-        <v>698.3061609510928</v>
+        <v>691.7600951639013</v>
       </c>
       <c r="D75">
-        <v>1703.451160951093</v>
+        <v>1713.570095163901</v>
       </c>
       <c r="E75">
-        <v>167.2450000000001</v>
+        <v>183.9100000000001</v>
       </c>
       <c r="F75">
-        <v>1216.545</v>
+        <v>1233.21</v>
       </c>
       <c r="G75">
         <v>211.4</v>
@@ -7437,28 +7437,28 @@
         <v>241.475</v>
       </c>
       <c r="M75">
-        <v>77.9805345</v>
+        <v>79.04876100000001</v>
       </c>
       <c r="N75">
-        <v>163.4944655</v>
+        <v>162.426239</v>
       </c>
       <c r="O75">
-        <v>57.22306292499999</v>
+        <v>56.84918364999999</v>
       </c>
       <c r="P75">
-        <v>106.271402575</v>
+        <v>105.57705535</v>
       </c>
       <c r="Q75">
-        <v>184.671402575</v>
+        <v>183.97705535</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2278270422930767</v>
+        <v>0.2339394345796138</v>
       </c>
       <c r="T75">
-        <v>2.648715258569672</v>
+        <v>2.737658014062273</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.096606115209431</v>
+        <v>3.054760086625519</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0916563529906996</v>
+        <v>0.0913839545622685</v>
       </c>
       <c r="C76">
-        <v>691.7600951639013</v>
+        <v>685.3349658686593</v>
       </c>
       <c r="D76">
-        <v>1713.570095163901</v>
+        <v>1723.809965868659</v>
       </c>
       <c r="E76">
-        <v>183.9100000000001</v>
+        <v>200.575</v>
       </c>
       <c r="F76">
-        <v>1233.21</v>
+        <v>1249.875</v>
       </c>
       <c r="G76">
         <v>211.4</v>
@@ -7519,28 +7519,28 @@
         <v>241.475</v>
       </c>
       <c r="M76">
-        <v>79.04876100000001</v>
+        <v>80.11698750000001</v>
       </c>
       <c r="N76">
-        <v>162.426239</v>
+        <v>161.3580125</v>
       </c>
       <c r="O76">
-        <v>56.84918364999999</v>
+        <v>56.47530437499999</v>
       </c>
       <c r="P76">
-        <v>105.57705535</v>
+        <v>104.882708125</v>
       </c>
       <c r="Q76">
-        <v>183.97705535</v>
+        <v>183.282708125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2339394345796138</v>
+        <v>0.240540818249074</v>
       </c>
       <c r="T76">
-        <v>2.737658014062273</v>
+        <v>2.833716189994283</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.054760086625519</v>
+        <v>3.014029952137179</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0913839545622685</v>
+        <v>0.0949647561338374</v>
       </c>
       <c r="C77">
-        <v>685.3349658686593</v>
+        <v>543.1202444774788</v>
       </c>
       <c r="D77">
-        <v>1723.809965868659</v>
+        <v>1598.260244477479</v>
       </c>
       <c r="E77">
-        <v>200.575</v>
+        <v>217.24</v>
       </c>
       <c r="F77">
-        <v>1249.875</v>
+        <v>1266.54</v>
       </c>
       <c r="G77">
         <v>211.4</v>
@@ -7601,45 +7601,45 @@
         <v>241.475</v>
       </c>
       <c r="M77">
-        <v>80.11698750000001</v>
+        <v>91.06422600000001</v>
       </c>
       <c r="N77">
-        <v>161.3580125</v>
+        <v>150.410774</v>
       </c>
       <c r="O77">
-        <v>56.47530437499999</v>
+        <v>52.6437709</v>
       </c>
       <c r="P77">
-        <v>104.882708125</v>
+        <v>97.76700310000001</v>
       </c>
       <c r="Q77">
-        <v>183.282708125</v>
+        <v>176.1670031</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.240540818249074</v>
+        <v>0.2476923172243225</v>
       </c>
       <c r="T77">
-        <v>2.833716189994283</v>
+        <v>2.937779213920627</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.014029952137179</v>
+        <v>2.651699911225293</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0949647561338374</v>
+        <v>0.09474305770540628</v>
       </c>
       <c r="C78">
-        <v>543.1202444774788</v>
+        <v>533.6949185198596</v>
       </c>
       <c r="D78">
-        <v>1598.260244477479</v>
+        <v>1605.499918519859</v>
       </c>
       <c r="E78">
-        <v>217.24</v>
+        <v>233.905</v>
       </c>
       <c r="F78">
-        <v>1266.54</v>
+        <v>1283.205</v>
       </c>
       <c r="G78">
         <v>211.4</v>
@@ -7683,28 +7683,28 @@
         <v>241.475</v>
       </c>
       <c r="M78">
-        <v>91.06422600000001</v>
+        <v>92.2624395</v>
       </c>
       <c r="N78">
-        <v>150.410774</v>
+        <v>149.2125605</v>
       </c>
       <c r="O78">
-        <v>52.6437709</v>
+        <v>52.224396175</v>
       </c>
       <c r="P78">
-        <v>97.76700310000001</v>
+        <v>96.988164325</v>
       </c>
       <c r="Q78">
-        <v>176.1670031</v>
+        <v>175.388164325</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2476923172243225</v>
+        <v>0.2554656856756795</v>
       </c>
       <c r="T78">
-        <v>2.937779213920627</v>
+        <v>3.050891196449262</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.651699911225293</v>
+        <v>2.617262250040548</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09474305770540628</v>
+        <v>0.09452135927697519</v>
       </c>
       <c r="C79">
-        <v>533.6949185198596</v>
+        <v>524.3354784234459</v>
       </c>
       <c r="D79">
-        <v>1605.499918519859</v>
+        <v>1612.805478423446</v>
       </c>
       <c r="E79">
-        <v>233.905</v>
+        <v>250.5700000000002</v>
       </c>
       <c r="F79">
-        <v>1283.205</v>
+        <v>1299.87</v>
       </c>
       <c r="G79">
         <v>211.4</v>
@@ -7765,28 +7765,28 @@
         <v>241.475</v>
       </c>
       <c r="M79">
-        <v>92.2624395</v>
+        <v>93.46065300000002</v>
       </c>
       <c r="N79">
-        <v>149.2125605</v>
+        <v>148.014347</v>
       </c>
       <c r="O79">
-        <v>52.224396175</v>
+        <v>51.80502144999999</v>
       </c>
       <c r="P79">
-        <v>96.988164325</v>
+        <v>96.20932554999999</v>
       </c>
       <c r="Q79">
-        <v>175.388164325</v>
+        <v>174.60932555</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2554656856756795</v>
+        <v>0.2639457239862508</v>
       </c>
       <c r="T79">
-        <v>3.050891196449262</v>
+        <v>3.174286086480499</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.617262250040548</v>
+        <v>2.583707605809259</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09452135927697519</v>
+        <v>0.09429966084854408</v>
       </c>
       <c r="C80">
-        <v>524.3354784234459</v>
+        <v>515.0428277074577</v>
       </c>
       <c r="D80">
-        <v>1612.805478423446</v>
+        <v>1620.177827707458</v>
       </c>
       <c r="E80">
-        <v>250.5700000000002</v>
+        <v>267.2350000000001</v>
       </c>
       <c r="F80">
-        <v>1299.87</v>
+        <v>1316.535</v>
       </c>
       <c r="G80">
         <v>211.4</v>
@@ -7847,28 +7847,28 @@
         <v>241.475</v>
       </c>
       <c r="M80">
-        <v>93.46065300000002</v>
+        <v>94.65886650000002</v>
       </c>
       <c r="N80">
-        <v>148.014347</v>
+        <v>146.8161335</v>
       </c>
       <c r="O80">
-        <v>51.80502144999999</v>
+        <v>51.38564672499999</v>
       </c>
       <c r="P80">
-        <v>96.20932554999999</v>
+        <v>95.43048677499999</v>
       </c>
       <c r="Q80">
-        <v>174.60932555</v>
+        <v>173.830486775</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2639457239862508</v>
+        <v>0.273233384993067</v>
       </c>
       <c r="T80">
-        <v>3.174286086480499</v>
+        <v>3.309432870800427</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.583707605809259</v>
+        <v>2.551002446242054</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09429966084854408</v>
+        <v>0.09407796242011296</v>
       </c>
       <c r="C81">
-        <v>515.0428277074577</v>
+        <v>505.8178864874042</v>
       </c>
       <c r="D81">
-        <v>1620.177827707458</v>
+        <v>1627.617886487404</v>
       </c>
       <c r="E81">
-        <v>267.2350000000001</v>
+        <v>283.9000000000001</v>
       </c>
       <c r="F81">
-        <v>1316.535</v>
+        <v>1333.2</v>
       </c>
       <c r="G81">
         <v>211.4</v>
@@ -7929,28 +7929,28 @@
         <v>241.475</v>
       </c>
       <c r="M81">
-        <v>94.65886650000002</v>
+        <v>95.85708000000001</v>
       </c>
       <c r="N81">
-        <v>146.8161335</v>
+        <v>145.61792</v>
       </c>
       <c r="O81">
-        <v>51.38564672499999</v>
+        <v>50.96627199999999</v>
       </c>
       <c r="P81">
-        <v>95.43048677499999</v>
+        <v>94.65164799999998</v>
       </c>
       <c r="Q81">
-        <v>173.830486775</v>
+        <v>173.051648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.273233384993067</v>
+        <v>0.2834498121005649</v>
       </c>
       <c r="T81">
-        <v>3.309432870800427</v>
+        <v>3.458094333552346</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.551002446242054</v>
+        <v>2.519114915664027</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09407796242011296</v>
+        <v>0.09590961399168188</v>
       </c>
       <c r="C82">
-        <v>505.8178864874042</v>
+        <v>429.6587371173207</v>
       </c>
       <c r="D82">
-        <v>1627.617886487404</v>
+        <v>1568.123737117321</v>
       </c>
       <c r="E82">
-        <v>283.9000000000001</v>
+        <v>300.5650000000001</v>
       </c>
       <c r="F82">
-        <v>1333.2</v>
+        <v>1349.865</v>
       </c>
       <c r="G82">
         <v>211.4</v>
@@ -8011,45 +8011,45 @@
         <v>241.475</v>
       </c>
       <c r="M82">
-        <v>95.85708000000001</v>
+        <v>102.319767</v>
       </c>
       <c r="N82">
-        <v>145.61792</v>
+        <v>139.155233</v>
       </c>
       <c r="O82">
-        <v>50.96627199999999</v>
+        <v>48.70433154999999</v>
       </c>
       <c r="P82">
-        <v>94.65164799999998</v>
+        <v>90.45090144999999</v>
       </c>
       <c r="Q82">
-        <v>173.051648</v>
+        <v>168.85090145</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2834498121005649</v>
+        <v>0.2947416525877994</v>
       </c>
       <c r="T82">
-        <v>3.458094333552346</v>
+        <v>3.622404371330784</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.519114915664027</v>
+        <v>2.360003419476121</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09590961399168188</v>
+        <v>0.09571326556325077</v>
       </c>
       <c r="C83">
-        <v>429.6587371173207</v>
+        <v>419.1624104728703</v>
       </c>
       <c r="D83">
-        <v>1568.123737117321</v>
+        <v>1574.29241047287</v>
       </c>
       <c r="E83">
-        <v>300.5650000000001</v>
+        <v>317.2300000000002</v>
       </c>
       <c r="F83">
-        <v>1349.865</v>
+        <v>1366.53</v>
       </c>
       <c r="G83">
         <v>211.4</v>
@@ -8093,28 +8093,28 @@
         <v>241.475</v>
       </c>
       <c r="M83">
-        <v>102.319767</v>
+        <v>103.582974</v>
       </c>
       <c r="N83">
-        <v>139.155233</v>
+        <v>137.892026</v>
       </c>
       <c r="O83">
-        <v>48.70433154999999</v>
+        <v>48.26220909999999</v>
       </c>
       <c r="P83">
-        <v>90.45090144999999</v>
+        <v>89.62981689999999</v>
       </c>
       <c r="Q83">
-        <v>168.85090145</v>
+        <v>168.0298169</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2947416525877994</v>
+        <v>0.3072881420180599</v>
       </c>
       <c r="T83">
-        <v>3.622404371330784</v>
+        <v>3.804971079973492</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.360003419476121</v>
+        <v>2.331222889970315</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09571326556325077</v>
+        <v>0.09551691713481966</v>
       </c>
       <c r="C84">
-        <v>419.1624104728703</v>
+        <v>408.7148080610825</v>
       </c>
       <c r="D84">
-        <v>1574.29241047287</v>
+        <v>1580.509808061083</v>
       </c>
       <c r="E84">
-        <v>317.2300000000002</v>
+        <v>333.8950000000002</v>
       </c>
       <c r="F84">
-        <v>1366.53</v>
+        <v>1383.195</v>
       </c>
       <c r="G84">
         <v>211.4</v>
@@ -8175,28 +8175,28 @@
         <v>241.475</v>
       </c>
       <c r="M84">
-        <v>103.582974</v>
+        <v>104.846181</v>
       </c>
       <c r="N84">
-        <v>137.892026</v>
+        <v>136.628819</v>
       </c>
       <c r="O84">
-        <v>48.26220909999999</v>
+        <v>47.82008664999999</v>
       </c>
       <c r="P84">
-        <v>89.62981689999999</v>
+        <v>88.80873234999999</v>
       </c>
       <c r="Q84">
-        <v>168.0298169</v>
+        <v>167.20873235</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3072881420180599</v>
+        <v>0.3213106890283511</v>
       </c>
       <c r="T84">
-        <v>3.804971079973492</v>
+        <v>4.009016224927109</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.331222889970315</v>
+        <v>2.303135867199588</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09551691713481966</v>
+        <v>0.09532056870638855</v>
       </c>
       <c r="C85">
-        <v>408.7148080610825</v>
+        <v>398.3165094548553</v>
       </c>
       <c r="D85">
-        <v>1580.509808061083</v>
+        <v>1586.776509454855</v>
       </c>
       <c r="E85">
-        <v>333.8950000000002</v>
+        <v>350.5600000000002</v>
       </c>
       <c r="F85">
-        <v>1383.195</v>
+        <v>1399.86</v>
       </c>
       <c r="G85">
         <v>211.4</v>
@@ -8257,28 +8257,28 @@
         <v>241.475</v>
       </c>
       <c r="M85">
-        <v>104.846181</v>
+        <v>106.109388</v>
       </c>
       <c r="N85">
-        <v>136.628819</v>
+        <v>135.365612</v>
       </c>
       <c r="O85">
-        <v>47.82008664999999</v>
+        <v>47.37796419999999</v>
       </c>
       <c r="P85">
-        <v>88.80873234999999</v>
+        <v>87.98764779999999</v>
       </c>
       <c r="Q85">
-        <v>167.20873235</v>
+        <v>166.3876478</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3213106890283511</v>
+        <v>0.3370860544149286</v>
       </c>
       <c r="T85">
-        <v>4.009016224927109</v>
+        <v>4.238567012999926</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.303135867199588</v>
+        <v>2.275717583066259</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09532056870638858</v>
+        <v>0.09512422027795747</v>
       </c>
       <c r="C86">
-        <v>398.3165094548547</v>
+        <v>387.9681034556745</v>
       </c>
       <c r="D86">
-        <v>1586.776509454854</v>
+        <v>1593.093103455674</v>
       </c>
       <c r="E86">
-        <v>350.5599999999999</v>
+        <v>367.2249999999999</v>
       </c>
       <c r="F86">
-        <v>1399.86</v>
+        <v>1416.525</v>
       </c>
       <c r="G86">
         <v>211.4</v>
@@ -8339,28 +8339,28 @@
         <v>241.475</v>
       </c>
       <c r="M86">
-        <v>106.109388</v>
+        <v>107.372595</v>
       </c>
       <c r="N86">
-        <v>135.365612</v>
+        <v>134.102405</v>
       </c>
       <c r="O86">
-        <v>47.37796419999999</v>
+        <v>46.93584174999999</v>
       </c>
       <c r="P86">
-        <v>87.9876478</v>
+        <v>87.16656325</v>
       </c>
       <c r="Q86">
-        <v>166.3876478</v>
+        <v>165.56656325</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3370860544149284</v>
+        <v>0.3549648018530497</v>
       </c>
       <c r="T86">
-        <v>4.238567012999924</v>
+        <v>4.498724572815783</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.27571758306626</v>
+        <v>2.248944435030186</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09512422027795747</v>
+        <v>0.09492787184952636</v>
       </c>
       <c r="C87">
-        <v>387.9681034556745</v>
+        <v>377.6701882780342</v>
       </c>
       <c r="D87">
-        <v>1593.093103455674</v>
+        <v>1599.460188278034</v>
       </c>
       <c r="E87">
-        <v>367.2249999999999</v>
+        <v>383.8900000000001</v>
       </c>
       <c r="F87">
-        <v>1416.525</v>
+        <v>1433.19</v>
       </c>
       <c r="G87">
         <v>211.4</v>
@@ -8421,28 +8421,28 @@
         <v>241.475</v>
       </c>
       <c r="M87">
-        <v>107.372595</v>
+        <v>108.635802</v>
       </c>
       <c r="N87">
-        <v>134.102405</v>
+        <v>132.839198</v>
       </c>
       <c r="O87">
-        <v>46.93584174999999</v>
+        <v>46.49371929999999</v>
       </c>
       <c r="P87">
-        <v>87.16656325</v>
+        <v>86.3454787</v>
       </c>
       <c r="Q87">
-        <v>165.56656325</v>
+        <v>164.7454787</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3549648018530497</v>
+        <v>0.3753976560680453</v>
       </c>
       <c r="T87">
-        <v>4.498724572815783</v>
+        <v>4.796047498319623</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.248944435030186</v>
+        <v>2.222793918343788</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09492787184952636</v>
+        <v>0.09473152342109525</v>
       </c>
       <c r="C88">
-        <v>377.6701882780342</v>
+        <v>367.4233717382924</v>
       </c>
       <c r="D88">
-        <v>1599.460188278034</v>
+        <v>1605.878371738292</v>
       </c>
       <c r="E88">
-        <v>383.8900000000001</v>
+        <v>400.5550000000001</v>
       </c>
       <c r="F88">
-        <v>1433.19</v>
+        <v>1449.855</v>
       </c>
       <c r="G88">
         <v>211.4</v>
@@ -8503,28 +8503,28 @@
         <v>241.475</v>
       </c>
       <c r="M88">
-        <v>108.635802</v>
+        <v>109.899009</v>
       </c>
       <c r="N88">
-        <v>132.839198</v>
+        <v>131.575991</v>
       </c>
       <c r="O88">
-        <v>46.49371929999999</v>
+        <v>46.05159685</v>
       </c>
       <c r="P88">
-        <v>86.3454787</v>
+        <v>85.52439414999999</v>
       </c>
       <c r="Q88">
-        <v>164.7454787</v>
+        <v>163.92439415</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3753976560680453</v>
+        <v>0.3989740263161172</v>
       </c>
       <c r="T88">
-        <v>4.796047498319623</v>
+        <v>5.139112412362514</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.222793918343788</v>
+        <v>2.197244562960527</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09473152342109525</v>
+        <v>0.09453517499266414</v>
       </c>
       <c r="C89">
-        <v>367.4233717382924</v>
+        <v>357.2282714480973</v>
       </c>
       <c r="D89">
-        <v>1605.878371738292</v>
+        <v>1612.348271448097</v>
       </c>
       <c r="E89">
-        <v>400.5550000000001</v>
+        <v>417.22</v>
       </c>
       <c r="F89">
-        <v>1449.855</v>
+        <v>1466.52</v>
       </c>
       <c r="G89">
         <v>211.4</v>
@@ -8585,28 +8585,28 @@
         <v>241.475</v>
       </c>
       <c r="M89">
-        <v>109.899009</v>
+        <v>111.162216</v>
       </c>
       <c r="N89">
-        <v>131.575991</v>
+        <v>130.312784</v>
       </c>
       <c r="O89">
-        <v>46.05159685</v>
+        <v>45.6094744</v>
       </c>
       <c r="P89">
-        <v>85.52439414999999</v>
+        <v>84.7033096</v>
       </c>
       <c r="Q89">
-        <v>163.92439415</v>
+        <v>163.1033096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3989740263161172</v>
+        <v>0.4264797916055345</v>
       </c>
       <c r="T89">
-        <v>5.139112412362514</v>
+        <v>5.539354812079221</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.197244562960527</v>
+        <v>2.172275874745066</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09453517499266414</v>
+        <v>0.09433882656423304</v>
       </c>
       <c r="C90">
-        <v>357.2282714480973</v>
+        <v>347.0855150125046</v>
       </c>
       <c r="D90">
-        <v>1612.348271448097</v>
+        <v>1618.870515012504</v>
       </c>
       <c r="E90">
-        <v>417.22</v>
+        <v>433.885</v>
       </c>
       <c r="F90">
-        <v>1466.52</v>
+        <v>1483.185</v>
       </c>
       <c r="G90">
         <v>211.4</v>
@@ -8667,28 +8667,28 @@
         <v>241.475</v>
       </c>
       <c r="M90">
-        <v>111.162216</v>
+        <v>112.425423</v>
       </c>
       <c r="N90">
-        <v>130.312784</v>
+        <v>129.049577</v>
       </c>
       <c r="O90">
-        <v>45.6094744</v>
+        <v>45.16735195</v>
       </c>
       <c r="P90">
-        <v>84.7033096</v>
+        <v>83.88222505</v>
       </c>
       <c r="Q90">
-        <v>163.1033096</v>
+        <v>162.28222505</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4264797916055345</v>
+        <v>0.4589866051293912</v>
       </c>
       <c r="T90">
-        <v>5.539354812079221</v>
+        <v>6.012368557198966</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.172275874745066</v>
+        <v>2.147868280646807</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09433882656423304</v>
+        <v>0.09414247813580193</v>
       </c>
       <c r="C91">
-        <v>347.0855150125046</v>
+        <v>336.9957402329251</v>
       </c>
       <c r="D91">
-        <v>1618.870515012504</v>
+        <v>1625.445740232925</v>
       </c>
       <c r="E91">
-        <v>433.885</v>
+        <v>450.5500000000002</v>
       </c>
       <c r="F91">
-        <v>1483.185</v>
+        <v>1499.85</v>
       </c>
       <c r="G91">
         <v>211.4</v>
@@ -8749,28 +8749,28 @@
         <v>241.475</v>
       </c>
       <c r="M91">
-        <v>112.425423</v>
+        <v>113.68863</v>
       </c>
       <c r="N91">
-        <v>129.049577</v>
+        <v>127.78637</v>
       </c>
       <c r="O91">
-        <v>45.16735195</v>
+        <v>44.72522949999999</v>
       </c>
       <c r="P91">
-        <v>83.88222505</v>
+        <v>83.06114049999999</v>
       </c>
       <c r="Q91">
-        <v>162.28222505</v>
+        <v>161.4611405</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4589866051293912</v>
+        <v>0.4979947813580194</v>
       </c>
       <c r="T91">
-        <v>6.012368557198966</v>
+        <v>6.57998505134266</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.147868280646807</v>
+        <v>2.124003077528509</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09414247813580193</v>
+        <v>0.09394612970737082</v>
       </c>
       <c r="C92">
-        <v>336.9957402329251</v>
+        <v>326.9595953150383</v>
       </c>
       <c r="D92">
-        <v>1625.445740232925</v>
+        <v>1632.074595315038</v>
       </c>
       <c r="E92">
-        <v>450.5500000000002</v>
+        <v>467.2150000000001</v>
       </c>
       <c r="F92">
-        <v>1499.85</v>
+        <v>1516.515</v>
       </c>
       <c r="G92">
         <v>211.4</v>
@@ -8831,28 +8831,28 @@
         <v>241.475</v>
       </c>
       <c r="M92">
-        <v>113.68863</v>
+        <v>114.951837</v>
       </c>
       <c r="N92">
-        <v>127.78637</v>
+        <v>126.523163</v>
       </c>
       <c r="O92">
-        <v>44.72522949999999</v>
+        <v>44.28310704999999</v>
       </c>
       <c r="P92">
-        <v>83.06114049999999</v>
+        <v>82.24005595</v>
       </c>
       <c r="Q92">
-        <v>161.4611405</v>
+        <v>160.64005595</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4979947813580194</v>
+        <v>0.5456714411930093</v>
       </c>
       <c r="T92">
-        <v>6.57998505134266</v>
+        <v>7.273738544184952</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.124003077528509</v>
+        <v>2.100662384368855</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09394612970737082</v>
+        <v>0.09374978127893971</v>
       </c>
       <c r="C93">
-        <v>326.9595953150383</v>
+        <v>316.9777390818108</v>
       </c>
       <c r="D93">
-        <v>1632.074595315038</v>
+        <v>1638.757739081811</v>
       </c>
       <c r="E93">
-        <v>467.2150000000001</v>
+        <v>483.8800000000001</v>
       </c>
       <c r="F93">
-        <v>1516.515</v>
+        <v>1533.18</v>
       </c>
       <c r="G93">
         <v>211.4</v>
@@ -8913,28 +8913,28 @@
         <v>241.475</v>
       </c>
       <c r="M93">
-        <v>114.951837</v>
+        <v>116.215044</v>
       </c>
       <c r="N93">
-        <v>126.523163</v>
+        <v>125.259956</v>
       </c>
       <c r="O93">
-        <v>44.28310704999999</v>
+        <v>43.84098459999999</v>
       </c>
       <c r="P93">
-        <v>82.24005595</v>
+        <v>81.41897139999998</v>
       </c>
       <c r="Q93">
-        <v>160.64005595</v>
+        <v>159.8189714</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5456714411930093</v>
+        <v>0.6052672659867466</v>
       </c>
       <c r="T93">
-        <v>7.273738544184952</v>
+        <v>8.140930410237818</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.100662384368855</v>
+        <v>2.077829097582237</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09374978127893971</v>
+        <v>0.0935534328505086</v>
       </c>
       <c r="C94">
-        <v>316.9777390818108</v>
+        <v>307.0508411917747</v>
       </c>
       <c r="D94">
-        <v>1638.757739081811</v>
+        <v>1645.495841191775</v>
       </c>
       <c r="E94">
-        <v>483.8800000000001</v>
+        <v>500.5450000000001</v>
       </c>
       <c r="F94">
-        <v>1533.18</v>
+        <v>1549.845</v>
       </c>
       <c r="G94">
         <v>211.4</v>
@@ -8995,28 +8995,28 @@
         <v>241.475</v>
       </c>
       <c r="M94">
-        <v>116.215044</v>
+        <v>117.478251</v>
       </c>
       <c r="N94">
-        <v>125.259956</v>
+        <v>123.996749</v>
       </c>
       <c r="O94">
-        <v>43.84098459999999</v>
+        <v>43.39886214999999</v>
       </c>
       <c r="P94">
-        <v>81.41897139999998</v>
+        <v>80.59788684999998</v>
       </c>
       <c r="Q94">
-        <v>159.8189714</v>
+        <v>158.99788685</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6052672659867466</v>
+        <v>0.6818904692929805</v>
       </c>
       <c r="T94">
-        <v>8.140930410237818</v>
+        <v>9.255891380877216</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.077829097582237</v>
+        <v>2.055486849221138</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0935534328505086</v>
+        <v>0.09335708442207752</v>
       </c>
       <c r="C95">
-        <v>307.0508411917747</v>
+        <v>297.1795823627092</v>
       </c>
       <c r="D95">
-        <v>1645.495841191775</v>
+        <v>1652.289582362709</v>
       </c>
       <c r="E95">
-        <v>500.5450000000001</v>
+        <v>517.21</v>
       </c>
       <c r="F95">
-        <v>1549.845</v>
+        <v>1566.51</v>
       </c>
       <c r="G95">
         <v>211.4</v>
@@ -9077,28 +9077,28 @@
         <v>241.475</v>
       </c>
       <c r="M95">
-        <v>117.478251</v>
+        <v>118.741458</v>
       </c>
       <c r="N95">
-        <v>123.996749</v>
+        <v>122.733542</v>
       </c>
       <c r="O95">
-        <v>43.39886214999999</v>
+        <v>42.95673969999999</v>
       </c>
       <c r="P95">
-        <v>80.59788684999998</v>
+        <v>79.77680229999999</v>
       </c>
       <c r="Q95">
-        <v>158.99788685</v>
+        <v>158.1768023</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6818904692929805</v>
+        <v>0.7840547403679591</v>
       </c>
       <c r="T95">
-        <v>9.255891380877216</v>
+        <v>10.74250600839642</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.055486849221138</v>
+        <v>2.033619967846445</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09335708442207752</v>
+        <v>0.09316073599364641</v>
       </c>
       <c r="C96">
-        <v>297.1795823627092</v>
+        <v>287.3646546008924</v>
       </c>
       <c r="D96">
-        <v>1652.289582362709</v>
+        <v>1659.139654600893</v>
       </c>
       <c r="E96">
-        <v>517.21</v>
+        <v>533.8750000000002</v>
       </c>
       <c r="F96">
-        <v>1566.51</v>
+        <v>1583.175</v>
       </c>
       <c r="G96">
         <v>211.4</v>
@@ -9159,28 +9159,28 @@
         <v>241.475</v>
       </c>
       <c r="M96">
-        <v>118.741458</v>
+        <v>120.004665</v>
       </c>
       <c r="N96">
-        <v>122.733542</v>
+        <v>121.470335</v>
       </c>
       <c r="O96">
-        <v>42.95673969999999</v>
+        <v>42.51461724999999</v>
       </c>
       <c r="P96">
-        <v>79.77680229999999</v>
+        <v>78.95571774999999</v>
       </c>
       <c r="Q96">
-        <v>158.1768023</v>
+        <v>157.35571775</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7840547403679591</v>
+        <v>0.9270847198729293</v>
       </c>
       <c r="T96">
-        <v>10.74250600839642</v>
+        <v>12.8237664869233</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.033619967846445</v>
+        <v>2.012213441869114</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09316073599364641</v>
+        <v>0.1018251875652153</v>
       </c>
       <c r="C97">
-        <v>287.3646546008924</v>
+        <v>14.10907788884992</v>
       </c>
       <c r="D97">
-        <v>1659.139654600893</v>
+        <v>1402.54907788885</v>
       </c>
       <c r="E97">
-        <v>533.8750000000002</v>
+        <v>550.5400000000002</v>
       </c>
       <c r="F97">
-        <v>1583.175</v>
+        <v>1599.84</v>
       </c>
       <c r="G97">
         <v>211.4</v>
@@ -9241,45 +9241,45 @@
         <v>241.475</v>
       </c>
       <c r="M97">
-        <v>120.004665</v>
+        <v>143.9856</v>
       </c>
       <c r="N97">
-        <v>121.470335</v>
+        <v>97.48939999999999</v>
       </c>
       <c r="O97">
-        <v>42.51461724999999</v>
+        <v>34.12128999999999</v>
       </c>
       <c r="P97">
-        <v>78.95571774999999</v>
+        <v>63.36810999999999</v>
       </c>
       <c r="Q97">
-        <v>157.35571775</v>
+        <v>141.76811</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9270847198729293</v>
+        <v>1.141629689130384</v>
       </c>
       <c r="T97">
-        <v>12.8237664869233</v>
+        <v>15.94565720471362</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.35</v>
       </c>
       <c r="W97">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.012213441869114</v>
+        <v>1.677077429965219</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1018251875652153</v>
+        <v>0.1017211391367842</v>
       </c>
       <c r="C98">
-        <v>14.10907788884992</v>
+        <v>0.05369975286225781</v>
       </c>
       <c r="D98">
-        <v>1402.54907788885</v>
+        <v>1405.158699752862</v>
       </c>
       <c r="E98">
-        <v>550.54</v>
+        <v>567.2049999999999</v>
       </c>
       <c r="F98">
-        <v>1599.84</v>
+        <v>1616.505</v>
       </c>
       <c r="G98">
         <v>211.4</v>
@@ -9323,28 +9323,28 @@
         <v>241.475</v>
       </c>
       <c r="M98">
-        <v>143.9856</v>
+        <v>145.48545</v>
       </c>
       <c r="N98">
-        <v>97.48940000000002</v>
+        <v>95.98955000000001</v>
       </c>
       <c r="O98">
-        <v>34.12129</v>
+        <v>33.5963425</v>
       </c>
       <c r="P98">
-        <v>63.36811000000002</v>
+        <v>62.39320750000001</v>
       </c>
       <c r="Q98">
-        <v>141.76811</v>
+        <v>140.7932075</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.141629689130382</v>
+        <v>1.499204637892805</v>
       </c>
       <c r="T98">
-        <v>15.94565720471358</v>
+        <v>21.14880840103077</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.677077429965219</v>
+        <v>1.65978797192434</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1017211391367842</v>
+        <v>0.1016170907083531</v>
       </c>
       <c r="C99">
-        <v>0.05369975286225781</v>
+        <v>-13.99194921056187</v>
       </c>
       <c r="D99">
-        <v>1405.158699752862</v>
+        <v>1407.778050789438</v>
       </c>
       <c r="E99">
-        <v>567.2049999999999</v>
+        <v>583.8700000000001</v>
       </c>
       <c r="F99">
-        <v>1616.505</v>
+        <v>1633.17</v>
       </c>
       <c r="G99">
         <v>211.4</v>
@@ -9405,28 +9405,28 @@
         <v>241.475</v>
       </c>
       <c r="M99">
-        <v>145.48545</v>
+        <v>146.9853</v>
       </c>
       <c r="N99">
-        <v>95.98955000000001</v>
+        <v>94.4897</v>
       </c>
       <c r="O99">
-        <v>33.5963425</v>
+        <v>33.071395</v>
       </c>
       <c r="P99">
-        <v>62.39320750000001</v>
+        <v>61.418305</v>
       </c>
       <c r="Q99">
-        <v>140.7932075</v>
+        <v>139.818305</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.499204637892805</v>
+        <v>2.214354535417653</v>
       </c>
       <c r="T99">
-        <v>21.14880840103077</v>
+        <v>31.55511079366513</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.65978797192434</v>
+        <v>1.642851359965928</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1016170907083531</v>
+        <v>0.101513042279922</v>
       </c>
       <c r="C100">
-        <v>-13.99194921056187</v>
+        <v>-28.02781449146846</v>
       </c>
       <c r="D100">
-        <v>1407.778050789438</v>
+        <v>1410.407185508531</v>
       </c>
       <c r="E100">
-        <v>583.8700000000001</v>
+        <v>600.5350000000001</v>
       </c>
       <c r="F100">
-        <v>1633.17</v>
+        <v>1649.835</v>
       </c>
       <c r="G100">
         <v>211.4</v>
@@ -9487,28 +9487,28 @@
         <v>241.475</v>
       </c>
       <c r="M100">
-        <v>146.9853</v>
+        <v>148.48515</v>
       </c>
       <c r="N100">
-        <v>94.4897</v>
+        <v>92.98984999999999</v>
       </c>
       <c r="O100">
-        <v>33.071395</v>
+        <v>32.54644749999999</v>
       </c>
       <c r="P100">
-        <v>61.418305</v>
+        <v>60.4434025</v>
       </c>
       <c r="Q100">
-        <v>139.818305</v>
+        <v>138.8434025</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.214354535417653</v>
+        <v>4.359804227992194</v>
       </c>
       <c r="T100">
-        <v>31.55511079366513</v>
+        <v>62.77401797156823</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.642851359965928</v>
+        <v>1.626256901784454</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.101513042279922</v>
-      </c>
-      <c r="C101">
-        <v>-28.02781449146846</v>
-      </c>
-      <c r="D101">
-        <v>1410.407185508531</v>
-      </c>
-      <c r="E101">
-        <v>600.5350000000001</v>
-      </c>
-      <c r="F101">
-        <v>1649.835</v>
-      </c>
-      <c r="G101">
-        <v>211.4</v>
-      </c>
-      <c r="H101">
-        <v>617.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>319.875</v>
-      </c>
-      <c r="K101">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>241.475</v>
-      </c>
-      <c r="M101">
-        <v>148.48515</v>
-      </c>
-      <c r="N101">
-        <v>92.98984999999999</v>
-      </c>
-      <c r="O101">
-        <v>32.54644749999999</v>
-      </c>
-      <c r="P101">
-        <v>60.4434025</v>
-      </c>
-      <c r="Q101">
-        <v>138.8434025</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.359804227992194</v>
-      </c>
-      <c r="T101">
-        <v>62.77401797156823</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.0585</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.626256901784454</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
